--- a/Models/Лошади/results/Лошади - Результаты прогнозов SARIMA.xlsx
+++ b/Models/Лошади/results/Лошади - Результаты прогнозов SARIMA.xlsx
@@ -488,12 +488,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -507,22 +507,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>97.11</v>
+        <v>35.72</v>
       </c>
       <c r="G2" t="n">
-        <v>76.08</v>
+        <v>29.12</v>
       </c>
       <c r="H2" t="n">
-        <v>7.44</v>
+        <v>2.77</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>[1609.65, 1076.2, 1052.86]</t>
+          <t>[937.45, 1323.07, 1002.4]</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>[1655.9, 915.95, 1074.61]</t>
+          <t>[995.56, 1304.96, 1013.53]</t>
         </is>
       </c>
     </row>
@@ -534,12 +534,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -553,22 +553,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>98.62</v>
+        <v>82.62</v>
       </c>
       <c r="G3" t="n">
-        <v>78.67</v>
+        <v>56.93</v>
       </c>
       <c r="H3" t="n">
-        <v>8.619999999999999</v>
+        <v>2.96</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>[1076.51, 1053.53, 906.89]</t>
+          <t>[1323.73, 1002.98, 2070.72]</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>[915.95, 1074.61, 852.53]</t>
+          <t>[1304.96, 1013.53, 2212.19]</t>
         </is>
       </c>
     </row>
@@ -580,12 +580,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -599,22 +599,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>50.37</v>
+        <v>89.06</v>
       </c>
       <c r="G4" t="n">
-        <v>46.89</v>
+        <v>70.7</v>
       </c>
       <c r="H4" t="n">
-        <v>4.69</v>
+        <v>3.55</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>[1052.5, 904.96, 1192.69]</t>
+          <t>[1002.82, 2070.27, 1816.62]</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>[1074.61, 852.53, 1126.55]</t>
+          <t>[1013.53, 2212.19, 1876.09]</t>
         </is>
       </c>
     </row>
@@ -626,12 +626,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -645,22 +645,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>116.45</v>
+        <v>93.13</v>
       </c>
       <c r="G5" t="n">
-        <v>100.57</v>
+        <v>83.37</v>
       </c>
       <c r="H5" t="n">
-        <v>6.88</v>
+        <v>4.21</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>[904.27, 1193.4, 1939.9]</t>
+          <t>[2070.41, 1816.82, 1659.39]</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>[852.53, 1126.55, 2123.03]</t>
+          <t>[2212.19, 1876.09, 1610.32]</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -691,22 +691,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>113.06</v>
+        <v>57.17</v>
       </c>
       <c r="G6" t="n">
-        <v>92.18000000000001</v>
+        <v>56.99</v>
       </c>
       <c r="H6" t="n">
-        <v>5.66</v>
+        <v>4.02</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>[1193.21, 1941.01, 1086.06]</t>
+          <t>[1818.26, 1661.44, 1004.98]</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>[1126.55, 2123.03, 1113.91]</t>
+          <t>[1876.09, 1610.32, 1067.0]</t>
         </is>
       </c>
     </row>
@@ -718,12 +718,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -737,22 +737,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>113</v>
+        <v>88.33</v>
       </c>
       <c r="G7" t="n">
-        <v>90.83</v>
+        <v>81.17</v>
       </c>
       <c r="H7" t="n">
-        <v>5.75</v>
+        <v>6.64</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>[1938.83, 1085.27, 935.89]</t>
+          <t>[1661.97, 1005.24, 1060.2]</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>[2123.03, 1113.91, 995.56]</t>
+          <t>[1610.32, 1067.0, 1190.29]</t>
         </is>
       </c>
     </row>
@@ -764,12 +764,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>38.6</v>
+        <v>85.7</v>
       </c>
       <c r="G8" t="n">
-        <v>34.49</v>
+        <v>75.41</v>
       </c>
       <c r="H8" t="n">
-        <v>3.23</v>
+        <v>6.79</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>[1086.68, 937.17, 1322.81]</t>
+          <t>[1005.94, 1059.41, 902.55]</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>[1113.91, 995.56, 1304.96]</t>
+          <t>[1067.0, 1190.29, 936.82]</t>
         </is>
       </c>
     </row>
@@ -810,12 +810,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -829,22 +829,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>35.72</v>
+        <v>100.38</v>
       </c>
       <c r="G9" t="n">
-        <v>29.12</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>2.77</v>
+        <v>8.17</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>[937.45, 1323.07, 1002.4]</t>
+          <t>[1056.79, 906.19, 1176.08]</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>[995.56, 1304.96, 1013.53]</t>
+          <t>[1190.29, 936.82, 1068.99]</t>
         </is>
       </c>
     </row>
@@ -856,12 +856,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -875,22 +875,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>82.62</v>
+        <v>70.03</v>
       </c>
       <c r="G10" t="n">
-        <v>56.93</v>
+        <v>62.49</v>
       </c>
       <c r="H10" t="n">
-        <v>2.96</v>
+        <v>5.28</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>[1323.73, 1002.98, 2070.72]</t>
+          <t>[904.24, 1175.22, 2057.38]</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>[1304.96, 1013.53, 2212.19]</t>
+          <t>[936.82, 1068.99, 2008.72]</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -921,22 +921,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>89.06</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>70.7</v>
+        <v>75.01000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>3.55</v>
+        <v>6.38</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>[1002.82, 2070.27, 1816.62]</t>
+          <t>[1176.3, 2055.15, 1121.35]</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>[1013.53, 2212.19, 1876.09]</t>
+          <t>[1068.99, 2008.72, 1050.06]</t>
         </is>
       </c>
     </row>
@@ -948,41 +948,41 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>(1, 1, 2)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>65.70999999999999</v>
+        <v>142.02</v>
       </c>
       <c r="G12" t="n">
-        <v>64.27</v>
+        <v>135.79</v>
       </c>
       <c r="H12" t="n">
-        <v>5.29</v>
+        <v>9.32</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>[1649.0, 830.29, 1638.35]</t>
+          <t>[1098.56, 1681.74, 2102.67]</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>[1595.0, 775.1, 1554.73]</t>
+          <t>[973.73, 1772.95, 1911.34]</t>
         </is>
       </c>
     </row>
@@ -994,17 +994,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>(1, 1, 2)</t>
+          <t>(3, 0, 1)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1013,22 +1013,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>73.09</v>
+        <v>126.04</v>
       </c>
       <c r="G13" t="n">
-        <v>69.98999999999999</v>
+        <v>123.96</v>
       </c>
       <c r="H13" t="n">
-        <v>5.77</v>
+        <v>5.81</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>[824.62, 1616.21, 1521.45]</t>
+          <t>[1624.38, 2004.95, 2990.43]</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>[775.1, 1554.73, 1422.49]</t>
+          <t>[1772.95, 1911.34, 3120.12]</t>
         </is>
       </c>
     </row>
@@ -1040,41 +1040,41 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>(1, 1, 2)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>152.57</v>
+        <v>465.53</v>
       </c>
       <c r="G14" t="n">
-        <v>119.61</v>
+        <v>339.09</v>
       </c>
       <c r="H14" t="n">
-        <v>8.26</v>
+        <v>8.76</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>[1595.2, 1488.07, 1185.67]</t>
+          <t>[2031.36, 3012.96, 5562.36]</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>[1554.73, 1422.49, 1438.45]</t>
+          <t>[1911.34, 3120.12, 4772.26]</t>
         </is>
       </c>
     </row>
@@ -1086,41 +1086,41 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>(1, 1, 2)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(1, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>229.52</v>
+        <v>363.02</v>
       </c>
       <c r="G15" t="n">
-        <v>204.88</v>
+        <v>307.32</v>
       </c>
       <c r="H15" t="n">
-        <v>11.29</v>
+        <v>8.91</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>[1481.84, 1173.98, 2279.09]</t>
+          <t>[2892.88, 5345.88, 1753.21]</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>[1422.49, 1438.45, 2569.91]</t>
+          <t>[3120.12, 4772.26, 1632.1]</t>
         </is>
       </c>
     </row>
@@ -1132,41 +1132,41 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>(1, 1, 2)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>248.19</v>
+        <v>436.39</v>
       </c>
       <c r="G16" t="n">
-        <v>224.39</v>
+        <v>349.16</v>
       </c>
       <c r="H16" t="n">
-        <v>12.65</v>
+        <v>13.66</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>[1166.09, 2246.43, 1126.07]</t>
+          <t>[5480.33, 1880.42, 925.53]</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>[1438.45, 2569.91, 1203.41]</t>
+          <t>[4772.26, 1632.1, 834.45]</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1197,22 +1197,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>138.7</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>83.98999999999999</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>3.45</v>
+        <v>4.39</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>[2329.93, 1214.52, 974.61]</t>
+          <t>[1777.36, 811.22, 1740.84]</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>[2569.91, 1203.41, 973.73]</t>
+          <t>[1632.1, 834.45, 1715.21]</t>
         </is>
       </c>
     </row>
@@ -1224,17 +1224,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>(3, 0, 1)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1243,22 +1243,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>105.06</v>
+        <v>105.97</v>
       </c>
       <c r="G18" t="n">
-        <v>97.47</v>
+        <v>76.05</v>
       </c>
       <c r="H18" t="n">
-        <v>8.41</v>
+        <v>4.48</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>[1342.03, 1082.83, 1728.28]</t>
+          <t>[828.25, 1671.39, 1579.36]</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>[1203.41, 973.73, 1772.95]</t>
+          <t>[834.45, 1715.21, 1757.48]</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1285,26 +1285,26 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>142.02</v>
+        <v>103.06</v>
       </c>
       <c r="G19" t="n">
-        <v>135.79</v>
+        <v>75.86</v>
       </c>
       <c r="H19" t="n">
-        <v>9.32</v>
+        <v>4.39</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>[1098.56, 1681.74, 2102.67]</t>
+          <t>[1673.98, 1584.3, 1444.53]</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>[973.73, 1772.95, 1911.34]</t>
+          <t>[1715.21, 1757.48, 1457.7]</t>
         </is>
       </c>
     </row>
@@ -1316,17 +1316,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>(3, 0, 1)</t>
+          <t>(2, 0, 2)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1335,22 +1335,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>126.04</v>
+        <v>151.48</v>
       </c>
       <c r="G20" t="n">
-        <v>123.96</v>
+        <v>102.76</v>
       </c>
       <c r="H20" t="n">
-        <v>5.81</v>
+        <v>5.92</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>[1624.38, 2004.95, 2990.43]</t>
+          <t>[1497.96, 1421.07, 2505.47]</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>[1772.95, 1911.34, 3120.12]</t>
+          <t>[1757.48, 1457.7, 2493.35]</t>
         </is>
       </c>
     </row>
@@ -1362,41 +1362,41 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>(2, 0, 0)</t>
+          <t>(2, 0, 2)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>465.53</v>
+        <v>132.09</v>
       </c>
       <c r="G21" t="n">
-        <v>339.09</v>
+        <v>119.17</v>
       </c>
       <c r="H21" t="n">
-        <v>8.76</v>
+        <v>6.41</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>[2031.36, 3012.96, 5562.36]</t>
+          <t>[1502.97, 2677.31, 1340.69]</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>[1911.34, 3120.12, 4772.26]</t>
+          <t>[1457.7, 2493.35, 1468.96]</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1427,22 +1427,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>330.45</v>
+        <v>60.76</v>
       </c>
       <c r="G22" t="n">
-        <v>289.71</v>
+        <v>60.28</v>
       </c>
       <c r="H22" t="n">
-        <v>26.3</v>
+        <v>3.43</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>[482.95, 415.94, 2483.4]</t>
+          <t>[1644.46, 2468.37, 1591.31]</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>[407.0, 752.27, 2940.25]</t>
+          <t>[1573.54, 2522.07, 1535.1]</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1473,22 +1473,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>443.86</v>
+        <v>64.08</v>
       </c>
       <c r="G23" t="n">
-        <v>398.46</v>
+        <v>54.96</v>
       </c>
       <c r="H23" t="n">
-        <v>29.66</v>
+        <v>2.39</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>[383.37, 2288.89, 808.77]</t>
+          <t>[2421.06, 1560.81, 2601.31]</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>[752.27, 2940.25, 983.9]</t>
+          <t>[2522.07, 1535.1, 2563.15]</t>
         </is>
       </c>
     </row>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1519,22 +1519,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>118.31</v>
+        <v>385.57</v>
       </c>
       <c r="G24" t="n">
-        <v>104.34</v>
+        <v>266.42</v>
       </c>
       <c r="H24" t="n">
-        <v>7.18</v>
+        <v>6.54</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>[3107.47, 1098.02, 777.74]</t>
+          <t>[1589.02, 2648.33, 4508.11]</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>[2940.25, 983.9, 746.07]</t>
+          <t>[1535.1, 2563.15, 5168.28]</t>
         </is>
       </c>
     </row>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1565,22 +1565,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>65.2</v>
+        <v>428.12</v>
       </c>
       <c r="G25" t="n">
-        <v>56.48</v>
+        <v>302.51</v>
       </c>
       <c r="H25" t="n">
-        <v>4.53</v>
+        <v>13.43</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>[1068.61, 756.9, 2023.81]</t>
+          <t>[2608.57, 4440.43, 415.21]</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>[983.9, 746.07, 2097.7]</t>
+          <t>[2563.15, 5168.28, 549.47]</t>
         </is>
       </c>
     </row>
@@ -1592,12 +1592,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1611,22 +1611,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>86.18000000000001</v>
+        <v>447.41</v>
       </c>
       <c r="G26" t="n">
-        <v>60.17</v>
+        <v>311.23</v>
       </c>
       <c r="H26" t="n">
-        <v>4.59</v>
+        <v>14.83</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>[729.4, 1950.27, 347.75]</t>
+          <t>[4406.41, 412.03, 761.56]</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>[746.07, 2097.7, 364.17]</t>
+          <t>[5168.28, 549.47, 727.18]</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1657,22 +1657,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>75.17</v>
+        <v>87.31999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>53.66</v>
+        <v>84.81</v>
       </c>
       <c r="H27" t="n">
-        <v>3.64</v>
+        <v>11.22</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>[1969.71, 351.22, 1593.58]</t>
+          <t>[441.78, 816.55, 3191.47]</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>[2097.7, 364.17, 1573.54]</t>
+          <t>[549.47, 727.18, 3248.83]</t>
         </is>
       </c>
     </row>
@@ -1684,12 +1684,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1703,22 +1703,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>52.18</v>
+        <v>217.4</v>
       </c>
       <c r="G28" t="n">
-        <v>43.61</v>
+        <v>213.55</v>
       </c>
       <c r="H28" t="n">
-        <v>2.49</v>
+        <v>17.45</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>[361.07, 1638.29, 2459.1]</t>
+          <t>[900.11, 3518.08, 1177.26]</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>[364.17, 1573.54, 2522.07]</t>
+          <t>[727.18, 3248.83, 978.78]</t>
         </is>
       </c>
     </row>
@@ -1730,12 +1730,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1745,26 +1745,26 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>60.76</v>
+        <v>64</v>
       </c>
       <c r="G29" t="n">
-        <v>60.28</v>
+        <v>57.65</v>
       </c>
       <c r="H29" t="n">
-        <v>3.43</v>
+        <v>4.67</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>[1644.46, 2468.37, 1591.31]</t>
+          <t>[3189.56, 1069.62, 810.54]</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>[1573.54, 2522.07, 1535.1]</t>
+          <t>[3248.83, 978.78, 787.7]</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1776,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1791,26 +1791,26 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>64.08</v>
+        <v>65.59</v>
       </c>
       <c r="G30" t="n">
-        <v>54.96</v>
+        <v>58.51</v>
       </c>
       <c r="H30" t="n">
-        <v>2.39</v>
+        <v>5.29</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>[2421.06, 1560.81, 2601.31]</t>
+          <t>[1077.84, 816.74, 2262.08]</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>[2522.07, 1535.1, 2563.15]</t>
+          <t>[978.78, 787.7, 2309.5]</t>
         </is>
       </c>
     </row>
@@ -1822,12 +1822,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1837,26 +1837,26 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>385.57</v>
+        <v>316.46</v>
       </c>
       <c r="G31" t="n">
-        <v>266.42</v>
+        <v>223.34</v>
       </c>
       <c r="H31" t="n">
-        <v>6.54</v>
+        <v>21.51</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>[1589.02, 2648.33, 4508.11]</t>
+          <t>[784.97, 2173.09, 379.88]</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>[1535.1, 2563.15, 5168.28]</t>
+          <t>[787.7, 2309.5, 910.76]</t>
         </is>
       </c>
     </row>
@@ -1868,17 +1868,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>(2, 0, 0)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1887,22 +1887,22 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>132.58</v>
+        <v>58.81</v>
       </c>
       <c r="G32" t="n">
-        <v>107.56</v>
+        <v>48.44</v>
       </c>
       <c r="H32" t="n">
-        <v>18.75</v>
+        <v>4.37</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>[693.33, 822.97, 795.24]</t>
+          <t>[688.47, 1268.25, 1119.61]</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>[484.2, 801.9, 887.7]</t>
+          <t>[683.3, 1181.92, 1065.8]</t>
         </is>
       </c>
     </row>
@@ -1914,12 +1914,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1933,22 +1933,22 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>77.48999999999999</v>
+        <v>66.22</v>
       </c>
       <c r="G33" t="n">
-        <v>70.51000000000001</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>9.17</v>
+        <v>5.38</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>[750.09, 771.96, 593.39]</t>
+          <t>[1265.78, 1118.99, 1354.44]</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>[801.9, 887.7, 549.4]</t>
+          <t>[1181.92, 1065.8, 1411.84]</t>
         </is>
       </c>
     </row>
@@ -1960,12 +1960,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1979,22 +1979,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>68.53</v>
+        <v>52.38</v>
       </c>
       <c r="G34" t="n">
-        <v>63.78</v>
+        <v>50.78</v>
       </c>
       <c r="H34" t="n">
-        <v>8.24</v>
+        <v>3.23</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>[788.56, 597.68, 968.12]</t>
+          <t>[1099.28, 1347.57, 2661.13]</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>[887.7, 549.4, 924.2]</t>
+          <t>[1065.8, 1411.84, 2715.72]</t>
         </is>
       </c>
     </row>
@@ -2006,12 +2006,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2025,22 +2025,22 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>56.7</v>
+        <v>61.23</v>
       </c>
       <c r="G35" t="n">
-        <v>56.08</v>
+        <v>59.84</v>
       </c>
       <c r="H35" t="n">
-        <v>7.82</v>
+        <v>5.13</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>[616.9, 977.2, 927.45]</t>
+          <t>[1336.65, 2654.87, 511.73]</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>[549.4, 924.2, 879.71]</t>
+          <t>[1411.84, 2715.72, 555.2]</t>
         </is>
       </c>
     </row>
@@ -2052,12 +2052,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2071,22 +2071,22 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>27.93</v>
+        <v>56.43</v>
       </c>
       <c r="G36" t="n">
-        <v>25.51</v>
+        <v>49.94</v>
       </c>
       <c r="H36" t="n">
-        <v>3.23</v>
+        <v>5.82</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>[948.63, 919.64, 498.35]</t>
+          <t>[2692.81, 513.81, 849.27]</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>[924.2, 879.71, 486.18]</t>
+          <t>[2715.72, 555.2, 934.8]</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2117,22 +2117,22 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>21.25</v>
+        <v>65.25</v>
       </c>
       <c r="G37" t="n">
-        <v>18.14</v>
+        <v>62.64</v>
       </c>
       <c r="H37" t="n">
-        <v>2.51</v>
+        <v>7.83</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>[913.48, 497.4, 692.73]</t>
+          <t>[514.94, 849.8, 939.9]</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>[879.71, 486.18, 683.3]</t>
+          <t>[555.2, 934.8, 877.25]</t>
         </is>
       </c>
     </row>
@@ -2144,12 +2144,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2163,22 +2163,22 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>50.87</v>
+        <v>74.02</v>
       </c>
       <c r="G38" t="n">
-        <v>33.82</v>
+        <v>73.61</v>
       </c>
       <c r="H38" t="n">
-        <v>3.27</v>
+        <v>9.24</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>[492.58, 690.81, 1269.47]</t>
+          <t>[866.62, 945.19, 582.8]</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>[486.18, 683.3, 1181.92]</t>
+          <t>[934.8, 877.25, 667.5]</t>
         </is>
       </c>
     </row>
@@ -2190,12 +2190,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2209,22 +2209,22 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>58.81</v>
+        <v>70.55</v>
       </c>
       <c r="G39" t="n">
-        <v>48.44</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="H39" t="n">
-        <v>4.37</v>
+        <v>8.25</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>[688.47, 1268.25, 1119.61]</t>
+          <t>[964.59, 586.28, 981.65]</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>[683.3, 1181.92, 1065.8]</t>
+          <t>[877.25, 667.5, 1008.2]</t>
         </is>
       </c>
     </row>
@@ -2236,12 +2236,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2255,22 +2255,22 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>66.22</v>
+        <v>134.89</v>
       </c>
       <c r="G40" t="n">
-        <v>64.81999999999999</v>
+        <v>113.16</v>
       </c>
       <c r="H40" t="n">
-        <v>5.38</v>
+        <v>15.62</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>[1265.78, 1118.99, 1354.44]</t>
+          <t>[572.02, 974.79, 930.84]</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>[1181.92, 1065.8, 1411.84]</t>
+          <t>[667.5, 1008.2, 720.25]</t>
         </is>
       </c>
     </row>
@@ -2282,12 +2282,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2301,22 +2301,22 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>52.38</v>
+        <v>128.03</v>
       </c>
       <c r="G41" t="n">
-        <v>50.78</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="H41" t="n">
-        <v>3.23</v>
+        <v>12.01</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>[1099.28, 1347.57, 2661.13]</t>
+          <t>[1012.6, 940.6, 516.84]</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>[1065.8, 1411.84, 2715.72]</t>
+          <t>[1008.2, 720.25, 492.3]</t>
         </is>
       </c>
     </row>
@@ -2328,12 +2328,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2347,22 +2347,22 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>160.78</v>
+        <v>265.41</v>
       </c>
       <c r="G42" t="n">
-        <v>104.95</v>
+        <v>222.12</v>
       </c>
       <c r="H42" t="n">
-        <v>18.63</v>
+        <v>10.93</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>[678.26, 832.09, 822.62]</t>
+          <t>[1958.21, 2763.8, 1832.29]</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>[702.95, 819.01, 545.55]</t>
+          <t>[1694.58, 2388.17, 1805.18]</t>
         </is>
       </c>
     </row>
@@ -2374,12 +2374,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2393,22 +2393,22 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>180.97</v>
+        <v>197.52</v>
       </c>
       <c r="G43" t="n">
-        <v>142.16</v>
+        <v>183.36</v>
       </c>
       <c r="H43" t="n">
-        <v>22.72</v>
+        <v>8.32</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>[851.6, 841.52, 1085.4]</t>
+          <t>[2513.0, 1666.85, 2088.51]</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>[819.01, 545.55, 987.47]</t>
+          <t>[2388.17, 1805.18, 2375.43]</t>
         </is>
       </c>
     </row>
@@ -2420,12 +2420,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2439,22 +2439,22 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>191.16</v>
+        <v>586.36</v>
       </c>
       <c r="G44" t="n">
-        <v>171.83</v>
+        <v>494.23</v>
       </c>
       <c r="H44" t="n">
-        <v>24.09</v>
+        <v>18.2</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>[822.1, 1058.94, 1335.43]</t>
+          <t>[1610.82, 2017.43, 2305.26]</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>[545.55, 987.47, 1167.97]</t>
+          <t>[1805.18, 2375.43, 3235.58]</t>
         </is>
       </c>
     </row>
@@ -2466,12 +2466,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2485,22 +2485,22 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>511.2</v>
+        <v>448.55</v>
       </c>
       <c r="G45" t="n">
-        <v>385.24</v>
+        <v>319.16</v>
       </c>
       <c r="H45" t="n">
-        <v>22.13</v>
+        <v>10.89</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>[824.77, 1035.11, 1372.03]</t>
+          <t>[2176.37, 2484.63, 686.89]</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>[987.47, 1167.97, 2232.18]</t>
+          <t>[2375.43, 3235.58, 694.36]</t>
         </is>
       </c>
     </row>
@@ -2512,12 +2512,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2531,22 +2531,22 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>500.54</v>
+        <v>350.4</v>
       </c>
       <c r="G46" t="n">
-        <v>405.6</v>
+        <v>225.72</v>
       </c>
       <c r="H46" t="n">
-        <v>21.52</v>
+        <v>9.27</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>[1166.7, 1544.16, 1040.87]</t>
+          <t>[2630.85, 728.01, 871.84]</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>[1167.97, 2232.18, 1568.38]</t>
+          <t>[3235.58, 694.36, 910.63]</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2577,22 +2577,22 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>533.28</v>
+        <v>155.29</v>
       </c>
       <c r="G47" t="n">
-        <v>512.04</v>
+        <v>146.85</v>
       </c>
       <c r="H47" t="n">
-        <v>27.8</v>
+        <v>21.88</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>[1545.49, 1041.51, 1372.03]</t>
+          <t>[833.86, 999.63, 804.62]</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>[2232.18, 1568.38, 1694.58]</t>
+          <t>[694.36, 910.63, 592.57]</t>
         </is>
       </c>
     </row>
@@ -2604,12 +2604,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2623,22 +2623,22 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>151.82</v>
+        <v>80.31</v>
       </c>
       <c r="G48" t="n">
-        <v>123.26</v>
+        <v>67.69</v>
       </c>
       <c r="H48" t="n">
-        <v>7.28</v>
+        <v>9.69</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>[1320.08, 1747.63, 2456.6]</t>
+          <t>[886.09, 719.31, 1093.37]</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>[1568.38, 1694.58, 2388.17]</t>
+          <t>[910.63, 592.57, 1041.58]</t>
         </is>
       </c>
     </row>
@@ -2650,12 +2650,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2669,22 +2669,22 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>265.41</v>
+        <v>115.92</v>
       </c>
       <c r="G49" t="n">
-        <v>222.12</v>
+        <v>112.14</v>
       </c>
       <c r="H49" t="n">
-        <v>10.93</v>
+        <v>13.54</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>[1958.21, 2763.8, 1832.29]</t>
+          <t>[732.95, 1113.28, 1363.71]</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>[1694.58, 2388.17, 1805.18]</t>
+          <t>[592.57, 1041.58, 1239.36]</t>
         </is>
       </c>
     </row>
@@ -2696,12 +2696,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2715,22 +2715,22 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>197.52</v>
+        <v>282.97</v>
       </c>
       <c r="G50" t="n">
-        <v>183.36</v>
+        <v>196.93</v>
       </c>
       <c r="H50" t="n">
-        <v>8.32</v>
+        <v>10.06</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>[2513.0, 1666.85, 2088.51]</t>
+          <t>[979.33, 1194.94, 1863.52]</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>[2388.17, 1805.18, 2375.43]</t>
+          <t>[1041.58, 1239.36, 2347.63]</t>
         </is>
       </c>
     </row>
@@ -2742,12 +2742,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2761,22 +2761,22 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>586.36</v>
+        <v>269.2</v>
       </c>
       <c r="G51" t="n">
-        <v>494.23</v>
+        <v>213.86</v>
       </c>
       <c r="H51" t="n">
-        <v>18.2</v>
+        <v>10.8</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>[1610.82, 2017.43, 2305.26]</t>
+          <t>[1244.67, 1942.99, 1339.03]</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>[1805.18, 2375.43, 3235.58]</t>
+          <t>[1239.36, 2347.63, 1570.65]</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2803,17 +2803,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>7.698804678135037e+18</v>
+        <v>2.246127103335071e+18</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>[0.0, 0.7, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2834,12 +2834,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2849,17 +2849,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>4.008280528333532e+18</v>
+        <v>1.364975126011735e+18</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>[0.7, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2880,41 +2880,41 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>0.4</v>
+        <v>0.23</v>
       </c>
       <c r="G54" t="n">
-        <v>0.23</v>
+        <v>0.13</v>
       </c>
       <c r="H54" t="n">
-        <v>9.247298684434897e+18</v>
+        <v>1.065107987307602e+18</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, -0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.7]</t>
+          <t>[0.0, 0.0, 0.4]</t>
         </is>
       </c>
     </row>
@@ -2926,41 +2926,41 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>0.96</v>
+        <v>0.23</v>
       </c>
       <c r="G55" t="n">
-        <v>0.73</v>
+        <v>0.13</v>
       </c>
       <c r="H55" t="n">
-        <v>1.067866788425175e+19</v>
+        <v>3.06769087371108e+19</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>[0.0, -0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>[0.0, 0.7, 1.5]</t>
+          <t>[0.0, 0.4, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2972,41 +2972,41 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>0.96</v>
+        <v>0.23</v>
       </c>
       <c r="G56" t="n">
-        <v>0.73</v>
+        <v>0.14</v>
       </c>
       <c r="H56" t="n">
-        <v>6.450205049150187e+16</v>
+        <v>5.64198590592203e+20</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>[-0.0, 0.0, -0.0]</t>
+          <t>[0.0, 0.0, 0.01]</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>[0.7, 1.5, 0.0]</t>
+          <t>[0.4, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -3018,17 +3018,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3037,22 +3037,22 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>0.87</v>
+        <v>0.23</v>
       </c>
       <c r="G57" t="n">
-        <v>0.5</v>
+        <v>0.14</v>
       </c>
       <c r="H57" t="n">
-        <v>9.811257539886141e+16</v>
+        <v>1.326047781577171e+21</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>[0.0, -0.0, -0.0]</t>
+          <t>[0.0, 0.02, 0.0]</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>[1.5, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.4]</t>
         </is>
       </c>
     </row>
@@ -3064,12 +3064,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3079,26 +3079,26 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(2, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="H58" t="n">
-        <v>2.189160314469723e+18</v>
+        <v>6.800354737181067e+20</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.01, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.4, 0.0]</t>
         </is>
       </c>
     </row>
@@ -3110,12 +3110,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3125,26 +3125,26 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(2, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="H59" t="n">
-        <v>2.246127103335071e+18</v>
+        <v>1.259110879402411e+21</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.02]</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.4, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3171,26 +3171,26 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(2, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="H60" t="n">
-        <v>1.364975126011735e+18</v>
+        <v>1.760208992006324e+21</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.02, 0.0]</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 1.5]</t>
         </is>
       </c>
     </row>
@@ -3202,12 +3202,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3221,13 +3221,13 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>0.23</v>
+        <v>1.54</v>
       </c>
       <c r="G61" t="n">
-        <v>0.13</v>
+        <v>1.23</v>
       </c>
       <c r="H61" t="n">
-        <v>1.065107987307602e+18</v>
+        <v>3.361118468688122e+20</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.4]</t>
+          <t>[0.0, 1.5, 2.2]</t>
         </is>
       </c>
     </row>
@@ -3248,12 +3248,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3267,22 +3267,22 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1.02</v>
+        <v>0.51</v>
       </c>
       <c r="G62" t="n">
-        <v>0.9</v>
+        <v>0.42</v>
       </c>
       <c r="H62" t="n">
-        <v>25.27</v>
+        <v>21.96</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>[2.61, 1.62, 3.23]</t>
+          <t>[2.4, 1.79, 2.64]</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>[3.9, 1.4, 4.4]</t>
+          <t>[1.8, 1.8, 2.0]</t>
         </is>
       </c>
     </row>
@@ -3294,12 +3294,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3313,22 +3313,22 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>0.87</v>
+        <v>0.62</v>
       </c>
       <c r="G63" t="n">
-        <v>0.78</v>
+        <v>0.5</v>
       </c>
       <c r="H63" t="n">
-        <v>37.49</v>
+        <v>19.52</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>[1.75, 3.67, 3.08]</t>
+          <t>[1.71, 2.4, 4.0]</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>[1.4, 4.4, 1.8]</t>
+          <t>[1.8, 2.0, 3.0]</t>
         </is>
       </c>
     </row>
@@ -3340,12 +3340,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3359,22 +3359,22 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>0.88</v>
+        <v>1.3</v>
       </c>
       <c r="G64" t="n">
-        <v>0.87</v>
+        <v>1.15</v>
       </c>
       <c r="H64" t="n">
-        <v>38.87</v>
+        <v>29.63</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>[3.54, 2.86, 2.49]</t>
+          <t>[2.43, 4.07, 8.04]</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>[4.4, 1.8, 1.8]</t>
+          <t>[2.0, 3.0, 6.1]</t>
         </is>
       </c>
     </row>
@@ -3386,12 +3386,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3405,22 +3405,22 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.66</v>
       </c>
       <c r="G65" t="n">
-        <v>0.92</v>
+        <v>1.55</v>
       </c>
       <c r="H65" t="n">
-        <v>57.92</v>
+        <v>33.52</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>[2.97, 2.67, 1.93]</t>
+          <t>[3.94, 7.5, 2.68]</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>[1.8, 1.8, 1.2]</t>
+          <t>[3.0, 6.1, 5.0]</t>
         </is>
       </c>
     </row>
@@ -3432,12 +3432,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3451,22 +3451,22 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>0.5</v>
+        <v>1.62</v>
       </c>
       <c r="G66" t="n">
-        <v>0.48</v>
+        <v>1.25</v>
       </c>
       <c r="H66" t="n">
-        <v>35.94</v>
+        <v>25.15</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>[2.46, 1.63, 1.34]</t>
+          <t>[7.17, 2.41, 1.5]</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>[1.8, 1.2, 0.99]</t>
+          <t>[6.1, 5.0, 1.6]</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3497,22 +3497,22 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.55</v>
       </c>
       <c r="G67" t="n">
-        <v>0.48</v>
+        <v>1.08</v>
       </c>
       <c r="H67" t="n">
-        <v>33.4</v>
+        <v>25.3</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>[1.55, 1.21, 2.67]</t>
+          <t>[2.35, 1.42, 3.18]</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>[1.2, 0.99, 1.8]</t>
+          <t>[5.0, 1.6, 3.6]</t>
         </is>
       </c>
     </row>
@@ -3524,12 +3524,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3543,22 +3543,22 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>0.4</v>
+        <v>0.34</v>
       </c>
       <c r="G68" t="n">
-        <v>0.31</v>
+        <v>0.24</v>
       </c>
       <c r="H68" t="n">
-        <v>19.39</v>
+        <v>7.78</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>[1.15, 2.47, 1.89]</t>
+          <t>[1.64, 4.18, 2.41]</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>[0.99, 1.8, 1.8]</t>
+          <t>[1.6, 3.6, 2.3]</t>
         </is>
       </c>
     </row>
@@ -3570,12 +3570,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3589,22 +3589,22 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>0.51</v>
+        <v>0.37</v>
       </c>
       <c r="G69" t="n">
-        <v>0.42</v>
+        <v>0.31</v>
       </c>
       <c r="H69" t="n">
-        <v>21.96</v>
+        <v>11.92</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>[2.4, 1.79, 2.64]</t>
+          <t>[4.16, 2.39, 2.09]</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>[1.8, 1.8, 2.0]</t>
+          <t>[3.6, 2.3, 1.8]</t>
         </is>
       </c>
     </row>
@@ -3616,12 +3616,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3635,22 +3635,22 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>0.62</v>
+        <v>0.2</v>
       </c>
       <c r="G70" t="n">
-        <v>0.5</v>
+        <v>0.17</v>
       </c>
       <c r="H70" t="n">
-        <v>19.52</v>
+        <v>9.27</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>[1.71, 2.4, 4.0]</t>
+          <t>[2.33, 2.0, 1.53]</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>[1.8, 2.0, 3.0]</t>
+          <t>[2.3, 1.8, 1.8]</t>
         </is>
       </c>
     </row>
@@ -3662,12 +3662,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3681,22 +3681,22 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1.3</v>
+        <v>0.36</v>
       </c>
       <c r="G71" t="n">
-        <v>1.15</v>
+        <v>0.34</v>
       </c>
       <c r="H71" t="n">
-        <v>29.63</v>
+        <v>38.26</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>[2.43, 4.07, 8.04]</t>
+          <t>[2.0, 1.52, 1.13]</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>[2.0, 3.0, 6.1]</t>
+          <t>[1.8, 1.8, 0.6]</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3727,22 +3727,22 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>20.15</v>
+        <v>341.21</v>
       </c>
       <c r="G72" t="n">
-        <v>17.59</v>
+        <v>245.89</v>
       </c>
       <c r="H72" t="n">
-        <v>17.76</v>
+        <v>160.12</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>[139.71, 73.52, 52.68]</t>
+          <t>[48.19, 36.39, 214.44]</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>[113.99, 96.8, 56.44]</t>
+          <t>[614.17, 34.8, 44.34]</t>
         </is>
       </c>
     </row>
@@ -3754,17 +3754,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(0, 0, 1)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3773,22 +3773,22 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>16.7</v>
+        <v>118.09</v>
       </c>
       <c r="G73" t="n">
-        <v>13.28</v>
+        <v>101.2</v>
       </c>
       <c r="H73" t="n">
-        <v>18.33</v>
+        <v>222.12</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>[69.29, 51.65, 49.24]</t>
+          <t>[69.07, 225.87, 143.21]</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>[96.8, 56.44, 41.7]</t>
+          <t>[34.8, 44.34, 55.41]</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3819,22 +3819,22 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>7.41</v>
+        <v>120.24</v>
       </c>
       <c r="G74" t="n">
-        <v>6.17</v>
+        <v>109.31</v>
       </c>
       <c r="H74" t="n">
-        <v>14.27</v>
+        <v>212.97</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>[56.82, 50.81, 53.51]</t>
+          <t>[223.21, 141.52, 141.57]</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>[56.44, 41.7, 44.48]</t>
+          <t>[44.34, 55.41, 78.62]</t>
         </is>
       </c>
     </row>
@@ -3846,41 +3846,41 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>8.289999999999999</v>
+        <v>46.63</v>
       </c>
       <c r="G75" t="n">
-        <v>8.210000000000001</v>
+        <v>45.24</v>
       </c>
       <c r="H75" t="n">
-        <v>21.2</v>
+        <v>63.69</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>[50.71, 53.48, 37.02]</t>
+          <t>[102.14, 109.32, 144.37]</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>[41.7, 44.48, 30.4]</t>
+          <t>[55.41, 78.62, 86.1]</t>
         </is>
       </c>
     </row>
@@ -3892,41 +3892,41 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(0, 0, 1)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>8.380000000000001</v>
+        <v>43.82</v>
       </c>
       <c r="G76" t="n">
-        <v>7.94</v>
+        <v>40.53</v>
       </c>
       <c r="H76" t="n">
-        <v>17.29</v>
+        <v>55.13</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>[50.6, 36.36, 75.14]</t>
+          <t>[96.72, 144.01, 106.29]</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>[44.48, 30.4, 63.4]</t>
+          <t>[78.62, 86.1, 60.7]</t>
         </is>
       </c>
     </row>
@@ -3938,41 +3938,41 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(0, 0, 1)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>325.5</v>
+        <v>41.91</v>
       </c>
       <c r="G77" t="n">
-        <v>193.05</v>
+        <v>39.97</v>
       </c>
       <c r="H77" t="n">
-        <v>41.38</v>
+        <v>61.1</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>[35.04, 74.24, 50.52]</t>
+          <t>[138.15, 105.98, 69.38]</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>[30.4, 63.4, 614.17]</t>
+          <t>[86.1, 60.7, 46.8]</t>
         </is>
       </c>
     </row>
@@ -3984,41 +3984,41 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(0, 0, 1)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>325.85</v>
+        <v>23.94</v>
       </c>
       <c r="G78" t="n">
-        <v>191.4</v>
+        <v>21.83</v>
       </c>
       <c r="H78" t="n">
-        <v>36.68</v>
+        <v>41.48</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>[71.27, 49.85, 36.8]</t>
+          <t>[94.76, 68.23, 54.41]</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>[63.4, 614.17, 34.8]</t>
+          <t>[60.7, 46.8, 44.4]</t>
         </is>
       </c>
     </row>
@@ -4030,41 +4030,41 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(0, 0, 1)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>341.21</v>
+        <v>16.1</v>
       </c>
       <c r="G79" t="n">
-        <v>245.89</v>
+        <v>15.25</v>
       </c>
       <c r="H79" t="n">
-        <v>160.12</v>
+        <v>37.93</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>[48.19, 36.39, 214.44]</t>
+          <t>[61.19, 53.8, 57.47]</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>[614.17, 34.8, 44.34]</t>
+          <t>[46.8, 44.4, 35.5]</t>
         </is>
       </c>
     </row>
@@ -4076,12 +4076,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4091,26 +4091,26 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>118.09</v>
+        <v>12.87</v>
       </c>
       <c r="G80" t="n">
-        <v>101.2</v>
+        <v>9.42</v>
       </c>
       <c r="H80" t="n">
-        <v>222.12</v>
+        <v>25.36</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>[69.07, 225.87, 143.21]</t>
+          <t>[50.23, 57.0, 39.51]</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>[34.8, 44.34, 55.41]</t>
+          <t>[44.4, 35.5, 38.6]</t>
         </is>
       </c>
     </row>
@@ -4122,41 +4122,41 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(0, 0, 1)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>120.24</v>
+        <v>20.77</v>
       </c>
       <c r="G81" t="n">
-        <v>109.31</v>
+        <v>16.86</v>
       </c>
       <c r="H81" t="n">
-        <v>212.97</v>
+        <v>39.56</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>[223.21, 141.52, 141.57]</t>
+          <t>[55.22, 39.37, 79.28]</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>[44.34, 55.41, 78.62]</t>
+          <t>[35.5, 38.6, 49.2]</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4187,22 +4187,22 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>71.34</v>
+        <v>57.68</v>
       </c>
       <c r="G82" t="n">
-        <v>69.40000000000001</v>
+        <v>41.53</v>
       </c>
       <c r="H82" t="n">
-        <v>5.79</v>
+        <v>1.97</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>[1485.62, 977.48, 1594.54]</t>
+          <t>[1725.15, 2205.63, 1396.97]</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>[1439.06, 901.1, 1509.3]</t>
+          <t>[1742.9, 2303.53, 1405.9]</t>
         </is>
       </c>
     </row>
@@ -4214,12 +4214,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4233,22 +4233,22 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>61.07</v>
+        <v>79.94</v>
       </c>
       <c r="G83" t="n">
-        <v>59.56</v>
+        <v>69.44</v>
       </c>
       <c r="H83" t="n">
-        <v>5.46</v>
+        <v>3.73</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>[961.44, 1585.01, 954.9]</t>
+          <t>[2208.79, 1392.41, 1736.17]</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>[901.1, 1509.3, 912.27]</t>
+          <t>[2303.53, 1405.9, 1636.1]</t>
         </is>
       </c>
     </row>
@@ -4260,12 +4260,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4279,22 +4279,22 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>62.19</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="G84" t="n">
-        <v>50.97</v>
+        <v>54.91</v>
       </c>
       <c r="H84" t="n">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>[1527.93, 945.95, 1410.17]</t>
+          <t>[1429.42, 1748.49, 1058.76]</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>[1509.3, 912.27, 1510.78]</t>
+          <t>[1405.9, 1636.1, 1029.92]</t>
         </is>
       </c>
     </row>
@@ -4306,17 +4306,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>(0, 1, 2)</t>
+          <t>(2, 0, 2)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4325,22 +4325,22 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>174.96</v>
+        <v>67.83</v>
       </c>
       <c r="G85" t="n">
-        <v>137.38</v>
+        <v>61.85</v>
       </c>
       <c r="H85" t="n">
-        <v>7.56</v>
+        <v>4.25</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>[936.53, 1406.32, 1877.28]</t>
+          <t>[1731.46, 1057.11, 1406.89]</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>[912.27, 1510.78, 2160.7]</t>
+          <t>[1636.1, 1029.92, 1469.9]</t>
         </is>
       </c>
     </row>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4367,26 +4367,26 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(1, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>179.68</v>
+        <v>52.81</v>
       </c>
       <c r="G86" t="n">
-        <v>150.64</v>
+        <v>42</v>
       </c>
       <c r="H86" t="n">
-        <v>9.74</v>
+        <v>3.47</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>[1383.86, 1880.02, 522.96]</t>
+          <t>[1033.48, 1387.96, 863.19]</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>[1510.78, 2160.7, 567.3]</t>
+          <t>[1029.92, 1469.9, 903.7]</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4413,26 +4413,26 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(1, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>110.66</v>
+        <v>75.12</v>
       </c>
       <c r="G87" t="n">
-        <v>91.33</v>
+        <v>72.67</v>
       </c>
       <c r="H87" t="n">
-        <v>6.08</v>
+        <v>5.51</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>[1981.68, 529.37, 1685.87]</t>
+          <t>[1381.78, 857.85, 1456.15]</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>[2160.7, 567.3, 1742.9]</t>
+          <t>[1469.9, 903.7, 1540.2]</t>
         </is>
       </c>
     </row>
@@ -4444,12 +4444,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4463,22 +4463,22 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>51.66</v>
+        <v>42.2</v>
       </c>
       <c r="G88" t="n">
-        <v>39</v>
+        <v>36.64</v>
       </c>
       <c r="H88" t="n">
-        <v>2.18</v>
+        <v>3.32</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>[558.74, 1720.71, 2217.28]</t>
+          <t>[913.57, 1501.14, 901.22]</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>[567.3, 1742.9, 2303.53]</t>
+          <t>[903.7, 1540.2, 962.22]</t>
         </is>
       </c>
     </row>
@@ -4490,12 +4490,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4509,22 +4509,22 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>57.68</v>
+        <v>48.79</v>
       </c>
       <c r="G89" t="n">
-        <v>41.53</v>
+        <v>46.99</v>
       </c>
       <c r="H89" t="n">
-        <v>1.97</v>
+        <v>3.86</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>[1725.15, 2205.63, 1396.97]</t>
+          <t>[1491.29, 900.2, 1495.25]</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>[1742.9, 2303.53, 1405.9]</t>
+          <t>[1540.2, 962.22, 1525.3]</t>
         </is>
       </c>
     </row>
@@ -4536,12 +4536,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4555,22 +4555,22 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>79.94</v>
+        <v>38.14</v>
       </c>
       <c r="G90" t="n">
-        <v>69.44</v>
+        <v>31.18</v>
       </c>
       <c r="H90" t="n">
-        <v>3.73</v>
+        <v>2.7</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>[2208.79, 1392.41, 1736.17]</t>
+          <t>[910.69, 1483.97, 2182.98]</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>[2303.53, 1405.9, 1636.1]</t>
+          <t>[962.22, 1525.3, 2182.3]</t>
         </is>
       </c>
     </row>
@@ -4582,12 +4582,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4601,22 +4601,22 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>68.34999999999999</v>
+        <v>49.15</v>
       </c>
       <c r="G91" t="n">
-        <v>54.91</v>
+        <v>42.88</v>
       </c>
       <c r="H91" t="n">
-        <v>3.78</v>
+        <v>4.82</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>[1429.42, 1748.49, 1058.76]</t>
+          <t>[1543.4, 2217.45, 571.42]</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>[1405.9, 1636.1, 1029.92]</t>
+          <t>[1525.3, 2182.3, 646.8]</t>
         </is>
       </c>
     </row>
@@ -4628,17 +4628,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4647,22 +4647,22 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>104.32</v>
+        <v>29.25</v>
       </c>
       <c r="G92" t="n">
-        <v>94.84</v>
+        <v>26.16</v>
       </c>
       <c r="H92" t="n">
-        <v>10.06</v>
+        <v>3.66</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>[780.81, 772.93, 934.35]</t>
+          <t>[572.67, 1379.18, 810.19]</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>[745.2, 883.08, 1073.09]</t>
+          <t>[609.67, 1386.95, 776.47]</t>
         </is>
       </c>
     </row>
@@ -4674,17 +4674,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -4693,22 +4693,22 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>112.95</v>
+        <v>28.12</v>
       </c>
       <c r="G93" t="n">
-        <v>99.18000000000001</v>
+        <v>23.87</v>
       </c>
       <c r="H93" t="n">
-        <v>10.13</v>
+        <v>2.5</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>[760.14, 922.87, 958.51]</t>
+          <t>[1412.25, 817.79, 1375.59]</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>[883.08, 1073.09, 982.9]</t>
+          <t>[1386.95, 776.47, 1380.59]</t>
         </is>
       </c>
     </row>
@@ -4720,12 +4720,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4739,22 +4739,22 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>60.77</v>
+        <v>202.67</v>
       </c>
       <c r="G94" t="n">
-        <v>54.63</v>
+        <v>131.18</v>
       </c>
       <c r="H94" t="n">
-        <v>5.51</v>
+        <v>5.55</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>[995.31, 1000.25, 985.16]</t>
+          <t>[812.21, 1371.89, 2707.33]</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>[1073.09, 982.9, 916.4]</t>
+          <t>[776.47, 1380.59, 3056.44]</t>
         </is>
       </c>
     </row>
@@ -4766,12 +4766,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4785,22 +4785,22 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>84.36</v>
+        <v>213.43</v>
       </c>
       <c r="G95" t="n">
-        <v>79.93000000000001</v>
+        <v>142.9</v>
       </c>
       <c r="H95" t="n">
-        <v>6.85</v>
+        <v>6.01</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>[1029.63, 996.65, 1717.16]</t>
+          <t>[1348.79, 2689.34, 772.69]</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>[982.9, 916.4, 1604.36]</t>
+          <t>[1380.59, 3056.44, 802.51]</t>
         </is>
       </c>
     </row>
@@ -4812,12 +4812,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>68.59</v>
+        <v>199.14</v>
       </c>
       <c r="G96" t="n">
-        <v>56.07</v>
+        <v>129.58</v>
       </c>
       <c r="H96" t="n">
-        <v>4.69</v>
+        <v>5.55</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>[979.16, 1705.12, 506.34]</t>
+          <t>[2713.07, 775.36, 918.26]</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>[916.4, 1604.36, 501.65]</t>
+          <t>[3056.44, 802.51, 900.05]</t>
         </is>
       </c>
     </row>
@@ -4858,12 +4858,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4877,22 +4877,22 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>40.02</v>
+        <v>55.66</v>
       </c>
       <c r="G97" t="n">
-        <v>31.96</v>
+        <v>44.21</v>
       </c>
       <c r="H97" t="n">
-        <v>3.26</v>
+        <v>4.52</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>[1662.98, 501.38, 572.68]</t>
+          <t>[810.99, 934.58, 1124.07]</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>[1604.36, 501.65, 609.67]</t>
+          <t>[802.51, 900.05, 1034.46]</t>
         </is>
       </c>
     </row>
@@ -4904,12 +4904,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4923,22 +4923,22 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>24.31</v>
+        <v>55.58</v>
       </c>
       <c r="G98" t="n">
-        <v>19.3</v>
+        <v>47.73</v>
       </c>
       <c r="H98" t="n">
-        <v>2.92</v>
+        <v>4.75</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>[494.56, 569.58, 1376.23]</t>
+          <t>[930.84, 1122.29, 1025.01]</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>[501.65, 609.67, 1386.95]</t>
+          <t>[900.05, 1034.46, 1049.59]</t>
         </is>
       </c>
     </row>
@@ -4950,12 +4950,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4969,22 +4969,22 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>29.25</v>
+        <v>53.63</v>
       </c>
       <c r="G99" t="n">
-        <v>26.16</v>
+        <v>50.48</v>
       </c>
       <c r="H99" t="n">
-        <v>3.66</v>
+        <v>4.92</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>[572.67, 1379.18, 810.19]</t>
+          <t>[1108.22, 1019.98, 952.65]</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>[609.67, 1386.95, 776.47]</t>
+          <t>[1034.46, 1049.59, 1000.72]</t>
         </is>
       </c>
     </row>
@@ -4996,12 +4996,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5015,22 +5015,22 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>28.12</v>
+        <v>46.29</v>
       </c>
       <c r="G100" t="n">
-        <v>23.87</v>
+        <v>37.81</v>
       </c>
       <c r="H100" t="n">
-        <v>2.5</v>
+        <v>3.69</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>[1412.25, 817.79, 1375.59]</t>
+          <t>[993.9, 943.05, 1661.68]</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>[1386.95, 776.47, 1380.59]</t>
+          <t>[1049.59, 1000.72, 1661.76]</t>
         </is>
       </c>
     </row>
@@ -5042,12 +5042,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5061,22 +5061,22 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>202.67</v>
+        <v>72.98</v>
       </c>
       <c r="G101" t="n">
-        <v>131.18</v>
+        <v>57.05</v>
       </c>
       <c r="H101" t="n">
-        <v>5.55</v>
+        <v>7.75</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>[812.21, 1371.89, 2707.33]</t>
+          <t>[962.48, 1674.91, 522.57]</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>[776.47, 1380.59, 3056.44]</t>
+          <t>[1000.72, 1661.76, 642.32]</t>
         </is>
       </c>
     </row>
@@ -5088,12 +5088,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5107,22 +5107,22 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>192.48</v>
+        <v>29.61</v>
       </c>
       <c r="G102" t="n">
-        <v>184.71</v>
+        <v>25.26</v>
       </c>
       <c r="H102" t="n">
-        <v>17.1</v>
+        <v>1.37</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>[1489.8, 825.68, 1420.44]</t>
+          <t>[1260.61, 2832.72, 1103.22]</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>[1268.71, 717.47, 1195.59]</t>
+          <t>[1277.95, 2785.86, 1091.65]</t>
         </is>
       </c>
     </row>
@@ -5134,12 +5134,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5153,22 +5153,22 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>148.78</v>
+        <v>43.54</v>
       </c>
       <c r="G103" t="n">
-        <v>137.68</v>
+        <v>38.11</v>
       </c>
       <c r="H103" t="n">
-        <v>12.8</v>
+        <v>1.94</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>[781.54, 1343.47, 973.86]</t>
+          <t>[2853.43, 1111.28, 1724.11]</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>[717.47, 1195.59, 1174.95]</t>
+          <t>[2785.86, 1091.65, 1696.98]</t>
         </is>
       </c>
     </row>
@@ -5180,12 +5180,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5199,22 +5199,22 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>181.15</v>
+        <v>46.63</v>
       </c>
       <c r="G104" t="n">
-        <v>169.4</v>
+        <v>30.66</v>
       </c>
       <c r="H104" t="n">
-        <v>14.28</v>
+        <v>0.67</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>[1283.89, 929.71, 1024.12]</t>
+          <t>[1097.52, 1702.75, 7134.23]</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>[1195.59, 1174.95, 1198.78]</t>
+          <t>[1091.65, 1696.98, 7053.88]</t>
         </is>
       </c>
     </row>
@@ -5226,12 +5226,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5245,22 +5245,22 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>497.42</v>
+        <v>36.72</v>
       </c>
       <c r="G105" t="n">
-        <v>425.73</v>
+        <v>26.94</v>
       </c>
       <c r="H105" t="n">
-        <v>21.47</v>
+        <v>0.78</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>[896.31, 987.66, 2625.0]</t>
+          <t>[1698.04, 7114.55, 1355.3]</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>[1174.95, 1198.78, 3412.44]</t>
+          <t>[1696.98, 7053.88, 1336.21]</t>
         </is>
       </c>
     </row>
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5291,22 +5291,22 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>267.97</v>
+        <v>36.04</v>
       </c>
       <c r="G106" t="n">
-        <v>230.93</v>
+        <v>29.61</v>
       </c>
       <c r="H106" t="n">
-        <v>13.91</v>
+        <v>1.25</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>[1125.95, 3007.74, 689.41]</t>
+          <t>[7112.28, 1354.86, 791.08]</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>[1198.78, 3412.44, 904.67]</t>
+          <t>[7053.88, 1336.21, 779.29]</t>
         </is>
       </c>
     </row>
@@ -5318,12 +5318,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5337,22 +5337,22 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>237.68</v>
+        <v>24.23</v>
       </c>
       <c r="G107" t="n">
-        <v>231.4</v>
+        <v>20.13</v>
       </c>
       <c r="H107" t="n">
-        <v>15.15</v>
+        <v>1.64</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>[3104.25, 711.81, 1084.8]</t>
+          <t>[1349.13, 787.75, 1319.96]</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>[3412.44, 904.67, 1277.95]</t>
+          <t>[1336.21, 779.29, 1358.98]</t>
         </is>
       </c>
     </row>
@@ -5364,12 +5364,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5383,22 +5383,22 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>174.51</v>
+        <v>266.03</v>
       </c>
       <c r="G108" t="n">
-        <v>170.69</v>
+        <v>169.53</v>
       </c>
       <c r="H108" t="n">
-        <v>11.9</v>
+        <v>10.42</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>[750.14, 1141.36, 2564.91]</t>
+          <t>[783.89, 1313.5, 1219.77]</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>[904.67, 1277.95, 2785.86]</t>
+          <t>[779.29, 1358.98, 1678.28]</t>
         </is>
       </c>
     </row>
@@ -5410,12 +5410,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5429,22 +5429,22 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>29.61</v>
+        <v>271</v>
       </c>
       <c r="G109" t="n">
-        <v>25.26</v>
+        <v>192.47</v>
       </c>
       <c r="H109" t="n">
-        <v>1.37</v>
+        <v>12.05</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>[1260.61, 2832.72, 1103.22]</t>
+          <t>[1309.47, 1216.18, 1256.5]</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>[1277.95, 2785.86, 1091.65]</t>
+          <t>[1358.98, 1678.28, 1322.31]</t>
         </is>
       </c>
     </row>
@@ -5456,12 +5456,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5475,22 +5475,22 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>43.54</v>
+        <v>259.97</v>
       </c>
       <c r="G110" t="n">
-        <v>38.11</v>
+        <v>189.96</v>
       </c>
       <c r="H110" t="n">
-        <v>1.94</v>
+        <v>10.58</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>[2853.43, 1111.28, 1724.11]</t>
+          <t>[1238.73, 1280.04, 3637.26]</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>[2785.86, 1091.65, 1696.98]</t>
+          <t>[1678.28, 1322.31, 3725.33]</t>
         </is>
       </c>
     </row>
@@ -5502,12 +5502,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5521,22 +5521,22 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>46.63</v>
+        <v>363.25</v>
       </c>
       <c r="G111" t="n">
-        <v>30.66</v>
+        <v>325.27</v>
       </c>
       <c r="H111" t="n">
-        <v>0.67</v>
+        <v>18.77</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>[1097.52, 1702.75, 7134.23]</t>
+          <t>[1504.37, 4276.63, 1116.29]</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>[1091.65, 1696.98, 7053.88]</t>
+          <t>[1322.31, 3725.33, 873.84]</t>
         </is>
       </c>
     </row>
@@ -5548,12 +5548,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5567,22 +5567,22 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>92.56999999999999</v>
+        <v>56.34</v>
       </c>
       <c r="G112" t="n">
-        <v>63.51</v>
+        <v>52.77</v>
       </c>
       <c r="H112" t="n">
-        <v>13.4</v>
+        <v>15.12</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>[403.83, 291.21, 382.37]</t>
+          <t>[451.96, 448.63, 305.82]</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>[394.91, 268.01, 540.77]</t>
+          <t>[371.41, 407.3, 269.39]</t>
         </is>
       </c>
     </row>
@@ -5594,12 +5594,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5613,22 +5613,22 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>95.11</v>
+        <v>23.71</v>
       </c>
       <c r="G113" t="n">
-        <v>70.95999999999999</v>
+        <v>23.61</v>
       </c>
       <c r="H113" t="n">
-        <v>17.2</v>
+        <v>7.78</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>[289.47, 380.42, 254.11]</t>
+          <t>[428.85, 292.1, 302.6]</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>[268.01, 540.77, 223.04]</t>
+          <t>[407.3, 269.39, 276.03]</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5659,22 +5659,22 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>101.4</v>
+        <v>27.13</v>
       </c>
       <c r="G114" t="n">
-        <v>68.20999999999999</v>
+        <v>26.05</v>
       </c>
       <c r="H114" t="n">
-        <v>14.76</v>
+        <v>6.77</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>[367.2, 249.4, 1269.69]</t>
+          <t>[288.22, 298.84, 686.88]</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>[540.77, 223.04, 1274.39]</t>
+          <t>[269.39, 276.03, 723.39]</t>
         </is>
       </c>
     </row>
@@ -5686,12 +5686,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5705,22 +5705,22 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>132.47</v>
+        <v>48.79</v>
       </c>
       <c r="G115" t="n">
-        <v>121.41</v>
+        <v>44.37</v>
       </c>
       <c r="H115" t="n">
-        <v>15.84</v>
+        <v>10.12</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>[272.21, 1414.7, 1382.8]</t>
+          <t>[294.07, 675.71, 323.7]</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>[223.04, 1274.39, 1208.04]</t>
+          <t>[276.03, 723.39, 391.11]</t>
         </is>
       </c>
     </row>
@@ -5732,17 +5732,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>(1, 1, 1)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -5751,22 +5751,22 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>108.64</v>
+        <v>58.66</v>
       </c>
       <c r="G116" t="n">
-        <v>105.37</v>
+        <v>57.01</v>
       </c>
       <c r="H116" t="n">
-        <v>16.95</v>
+        <v>13.88</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>[1407.14, 1321.77, 294.18]</t>
+          <t>[664.34, 318.27, 224.36]</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>[1274.39, 1208.04, 224.55]</t>
+          <t>[723.39, 391.11, 263.5]</t>
         </is>
       </c>
     </row>
@@ -5778,17 +5778,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>(0, 1, 2)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -5797,22 +5797,22 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>100.59</v>
+        <v>45.82</v>
       </c>
       <c r="G117" t="n">
-        <v>97.52</v>
+        <v>42.64</v>
       </c>
       <c r="H117" t="n">
-        <v>23.05</v>
+        <v>12.48</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>[1319.04, 287.46, 490.07]</t>
+          <t>[325.09, 229.19, 338.81]</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>[1208.04, 224.55, 371.41]</t>
+          <t>[391.11, 263.5, 366.41]</t>
         </is>
       </c>
     </row>
@@ -5824,17 +5824,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>(0, 1, 2)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -5843,22 +5843,22 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>82.83</v>
+        <v>18.36</v>
       </c>
       <c r="G118" t="n">
-        <v>80.26000000000001</v>
+        <v>17.63</v>
       </c>
       <c r="H118" t="n">
-        <v>24.59</v>
+        <v>6.62</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>[285.0, 479.89, 479.13]</t>
+          <t>[238.66, 353.06, 201.71]</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>[224.55, 371.41, 407.3]</t>
+          <t>[263.5, 366.41, 216.41]</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5889,22 +5889,22 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>56.34</v>
+        <v>63.82</v>
       </c>
       <c r="G119" t="n">
-        <v>52.77</v>
+        <v>42.01</v>
       </c>
       <c r="H119" t="n">
-        <v>15.12</v>
+        <v>5.14</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>[451.96, 448.63, 305.82]</t>
+          <t>[360.73, 205.96, 1104.26]</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>[371.41, 407.3, 269.39]</t>
+          <t>[366.41, 216.41, 1214.16]</t>
         </is>
       </c>
     </row>
@@ -5916,12 +5916,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5935,22 +5935,22 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>23.71</v>
+        <v>80.3</v>
       </c>
       <c r="G120" t="n">
-        <v>23.61</v>
+        <v>68.48</v>
       </c>
       <c r="H120" t="n">
-        <v>7.78</v>
+        <v>7.03</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>[428.85, 292.1, 302.6]</t>
+          <t>[206.39, 1107.7, 1065.88]</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>[407.3, 269.39, 276.03]</t>
+          <t>[216.41, 1214.16, 1154.83]</t>
         </is>
       </c>
     </row>
@@ -5962,12 +5962,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5981,22 +5981,22 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>27.13</v>
+        <v>71.19</v>
       </c>
       <c r="G121" t="n">
-        <v>26.05</v>
+        <v>64.77</v>
       </c>
       <c r="H121" t="n">
-        <v>6.77</v>
+        <v>8.01</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>[288.22, 298.84, 686.88]</t>
+          <t>[1120.1, 1078.88, 225.8]</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>[269.39, 276.03, 723.39]</t>
+          <t>[1214.16, 1154.83, 250.09]</t>
         </is>
       </c>
     </row>
@@ -6008,17 +6008,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>(2, 0, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -6027,22 +6027,22 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>133.25</v>
+        <v>239.91</v>
       </c>
       <c r="G122" t="n">
-        <v>116.2</v>
+        <v>239.62</v>
       </c>
       <c r="H122" t="n">
-        <v>15.44</v>
+        <v>31.02</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>[943.24, 814.62, 882.41]</t>
+          <t>[848.8, 1055.79, 1182.72]</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>[779.05, 790.61, 722.0]</t>
+          <t>[624.89, 803.3, 940.25]</t>
         </is>
       </c>
     </row>
@@ -6054,17 +6054,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>(2, 0, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -6073,22 +6073,22 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>100.28</v>
+        <v>180.56</v>
       </c>
       <c r="G123" t="n">
-        <v>82.28</v>
+        <v>180.49</v>
       </c>
       <c r="H123" t="n">
-        <v>11.33</v>
+        <v>20.91</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>[786.53, 824.8, 867.47]</t>
+          <t>[989.41, 1113.71, 1043.49]</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>[790.61, 722.0, 727.52]</t>
+          <t>[803.3, 940.25, 861.61]</t>
         </is>
       </c>
     </row>
@@ -6100,17 +6100,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>(2, 0, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -6119,22 +6119,22 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>112.04</v>
+        <v>107.24</v>
       </c>
       <c r="G124" t="n">
-        <v>109.38</v>
+        <v>98.16</v>
       </c>
       <c r="H124" t="n">
-        <v>15.32</v>
+        <v>10.39</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>[825.65, 869.03, 766.0]</t>
+          <t>[1060.23, 998.27, 1526.15]</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>[722.0, 727.52, 683.02]</t>
+          <t>[940.25, 861.61, 1488.29]</t>
         </is>
       </c>
     </row>
@@ -6146,17 +6146,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>(2, 0, 0)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -6165,22 +6165,22 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>196.37</v>
+        <v>62.86</v>
       </c>
       <c r="G125" t="n">
-        <v>154.71</v>
+        <v>47.35</v>
       </c>
       <c r="H125" t="n">
-        <v>16.08</v>
+        <v>5.45</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>[844.45, 712.15, 821.93]</t>
+          <t>[965.52, 1482.01, 789.63]</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>[727.52, 683.02, 1139.98]</t>
+          <t>[861.61, 1488.29, 821.5]</t>
         </is>
       </c>
     </row>
@@ -6192,17 +6192,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>(2, 0, 0)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -6211,22 +6211,22 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>228.79</v>
+        <v>48.69</v>
       </c>
       <c r="G126" t="n">
-        <v>171.56</v>
+        <v>47.54</v>
       </c>
       <c r="H126" t="n">
-        <v>15.52</v>
+        <v>4.79</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>[688.88, 768.2, 909.37]</t>
+          <t>[1433.24, 766.59, 786.41]</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>[683.02, 1139.98, 1046.42]</t>
+          <t>[1488.29, 821.5, 819.07]</t>
         </is>
       </c>
     </row>
@@ -6238,17 +6238,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>(2, 0, 0)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -6257,22 +6257,22 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>245.21</v>
+        <v>34.29</v>
       </c>
       <c r="G127" t="n">
-        <v>219.8</v>
+        <v>32.9</v>
       </c>
       <c r="H127" t="n">
-        <v>23.15</v>
+        <v>4.1</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>[766.46, 905.7, 770.03]</t>
+          <t>[774.99, 794.14, 731.41]</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>[1139.98, 1046.42, 624.89]</t>
+          <t>[821.5, 819.07, 758.66]</t>
         </is>
       </c>
     </row>
@@ -6284,12 +6284,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6303,22 +6303,22 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>188.72</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="G128" t="n">
-        <v>167.99</v>
+        <v>49.41</v>
       </c>
       <c r="H128" t="n">
-        <v>23</v>
+        <v>5.79</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>[999.02, 839.6, 1045.16]</t>
+          <t>[807.12, 742.29, 752.58]</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>[1046.42, 624.89, 803.3]</t>
+          <t>[819.07, 758.66, 872.49]</t>
         </is>
       </c>
     </row>
@@ -6330,12 +6330,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6349,22 +6349,22 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>239.91</v>
+        <v>103.04</v>
       </c>
       <c r="G129" t="n">
-        <v>239.62</v>
+        <v>88.15000000000001</v>
       </c>
       <c r="H129" t="n">
-        <v>31.02</v>
+        <v>12.78</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>[848.8, 1055.79, 1182.72]</t>
+          <t>[745.32, 755.37, 712.73]</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>[624.89, 803.3, 940.25]</t>
+          <t>[758.66, 872.49, 578.73]</t>
         </is>
       </c>
     </row>
@@ -6376,12 +6376,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6395,22 +6395,22 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>180.56</v>
+        <v>102.87</v>
       </c>
       <c r="G130" t="n">
-        <v>180.49</v>
+        <v>86.39</v>
       </c>
       <c r="H130" t="n">
-        <v>20.91</v>
+        <v>12.47</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>[989.41, 1113.71, 1043.49]</t>
+          <t>[759.08, 715.89, 1199.54]</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>[803.3, 940.25, 861.61]</t>
+          <t>[872.49, 578.73, 1190.92]</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6441,22 +6441,22 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>107.24</v>
+        <v>106.91</v>
       </c>
       <c r="G131" t="n">
-        <v>98.16</v>
+        <v>94.04000000000001</v>
       </c>
       <c r="H131" t="n">
-        <v>10.39</v>
+        <v>13</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>[1060.23, 998.27, 1526.15]</t>
+          <t>[743.98, 1240.58, 1137.87]</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>[940.25, 861.61, 1488.29]</t>
+          <t>[578.73, 1190.92, 1070.66]</t>
         </is>
       </c>
     </row>
@@ -6468,12 +6468,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6487,22 +6487,22 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>5.54</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="G132" t="n">
-        <v>3.46</v>
+        <v>61.46</v>
       </c>
       <c r="H132" t="n">
-        <v>3.52</v>
+        <v>12.38</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>[108.27, 136.25, 42.14]</t>
+          <t>[138.59, 402.67, 230.27]</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>[98.7, 135.6, 42.3]</t>
+          <t>[146.4, 574.9, 234.6]</t>
         </is>
       </c>
     </row>
@@ -6514,12 +6514,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6533,22 +6533,22 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>1.14</v>
+        <v>102.32</v>
       </c>
       <c r="G133" t="n">
-        <v>0.89</v>
+        <v>72.7</v>
       </c>
       <c r="H133" t="n">
-        <v>0.75</v>
+        <v>15.04</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>[136.25, 42.14, 131.64]</t>
+          <t>[402.67, 230.27, 353.13]</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>[135.6, 42.3, 133.5]</t>
+          <t>[574.9, 234.6, 311.6]</t>
         </is>
       </c>
     </row>
@@ -6560,12 +6560,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6579,22 +6579,22 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>1.08</v>
+        <v>35.17</v>
       </c>
       <c r="G134" t="n">
-        <v>0.73</v>
+        <v>27.41</v>
       </c>
       <c r="H134" t="n">
-        <v>0.65</v>
+        <v>8.08</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>[42.14, 131.64, 88.93]</t>
+          <t>[240.89, 369.41, 621.72]</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>[42.3, 133.5, 89.1]</t>
+          <t>[234.6, 311.6, 603.6]</t>
         </is>
       </c>
     </row>
@@ -6606,12 +6606,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6625,22 +6625,22 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>1.08</v>
+        <v>35.62</v>
       </c>
       <c r="G135" t="n">
-        <v>0.7</v>
+        <v>29.34</v>
       </c>
       <c r="H135" t="n">
-        <v>0.54</v>
+        <v>11.69</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>[131.64, 88.93, 328.72]</t>
+          <t>[369.32, 621.56, 103.22]</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>[133.5, 89.1, 328.8]</t>
+          <t>[311.6, 603.6, 90.9]</t>
         </is>
       </c>
     </row>
@@ -6652,12 +6652,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -6671,22 +6671,22 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>2.15</v>
+        <v>15.78</v>
       </c>
       <c r="G136" t="n">
-        <v>1.32</v>
+        <v>15.59</v>
       </c>
       <c r="H136" t="n">
-        <v>0.8</v>
+        <v>10.14</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>[88.93, 328.72, 167.28]</t>
+          <t>[620.58, 103.06, 141.59]</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>[89.1, 328.8, 171.0]</t>
+          <t>[603.6, 90.9, 123.95]</t>
         </is>
       </c>
     </row>
@@ -6698,12 +6698,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -6717,22 +6717,22 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>4.99</v>
+        <v>93.70999999999999</v>
       </c>
       <c r="G137" t="n">
-        <v>3.87</v>
+        <v>63.54</v>
       </c>
       <c r="H137" t="n">
-        <v>2.51</v>
+        <v>35.34</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>[328.72, 167.28, 138.59]</t>
+          <t>[103.03, 141.55, 44.16]</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>[328.8, 171.0, 146.4]</t>
+          <t>[90.9, 123.95, 205.05]</t>
         </is>
       </c>
     </row>
@@ -6744,12 +6744,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6763,22 +6763,22 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>99.56</v>
+        <v>93.56999999999999</v>
       </c>
       <c r="G138" t="n">
-        <v>61.25</v>
+        <v>62</v>
       </c>
       <c r="H138" t="n">
-        <v>12.49</v>
+        <v>32.78</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>[167.28, 138.59, 402.67]</t>
+          <t>[141.39, 44.11, 139.2]</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>[171.0, 146.4, 574.9]</t>
+          <t>[123.95, 205.05, 131.6]</t>
         </is>
       </c>
     </row>
@@ -6790,12 +6790,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -6809,22 +6809,22 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>99.56999999999999</v>
+        <v>109.78</v>
       </c>
       <c r="G139" t="n">
-        <v>61.46</v>
+        <v>89.78</v>
       </c>
       <c r="H139" t="n">
-        <v>12.38</v>
+        <v>45.42</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>[138.59, 402.67, 230.27]</t>
+          <t>[44.05, 139.04, 92.79]</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>[146.4, 574.9, 234.6]</t>
+          <t>[205.05, 131.6, 193.7]</t>
         </is>
       </c>
     </row>
@@ -6836,12 +6836,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -6855,22 +6855,22 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>102.32</v>
+        <v>62.52</v>
       </c>
       <c r="G140" t="n">
-        <v>72.7</v>
+        <v>50.13</v>
       </c>
       <c r="H140" t="n">
-        <v>15.04</v>
+        <v>24.03</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>[402.67, 230.27, 353.13]</t>
+          <t>[140.98, 94.09, 347.21]</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>[574.9, 234.6, 311.6]</t>
+          <t>[131.6, 193.7, 305.8]</t>
         </is>
       </c>
     </row>
@@ -6882,17 +6882,17 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(4, 0, 0)</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -6901,22 +6901,22 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>35.17</v>
+        <v>298.35</v>
       </c>
       <c r="G141" t="n">
-        <v>27.41</v>
+        <v>213.17</v>
       </c>
       <c r="H141" t="n">
-        <v>8.08</v>
+        <v>80.05</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>[240.89, 369.41, 621.72]</t>
+          <t>[118.16, 813.94, 103.77]</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>[234.6, 311.6, 603.6]</t>
+          <t>[193.7, 305.8, 159.6]</t>
         </is>
       </c>
     </row>
@@ -6928,41 +6928,41 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(1, 1, 0)</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>1907.41</v>
+        <v>116.73</v>
       </c>
       <c r="G142" t="n">
-        <v>1847.46</v>
+        <v>112.44</v>
       </c>
       <c r="H142" t="n">
-        <v>122.75</v>
+        <v>2.16</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>[3608.73, 3608.73, 3608.73]</t>
+          <t>[5615.67, 6519.12, 4067.94]</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>[1145.33, 1838.78, 2299.68]</t>
+          <t>[5536.26, 6364.54, 3964.6]</t>
         </is>
       </c>
     </row>
@@ -6974,41 +6974,41 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(1, 1, 0)</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>1216.14</v>
+        <v>693.6900000000001</v>
       </c>
       <c r="G143" t="n">
-        <v>1180.63</v>
+        <v>451.28</v>
       </c>
       <c r="H143" t="n">
-        <v>55.84</v>
+        <v>14.06</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>[3407.48, 3407.48, 3407.48]</t>
+          <t>[6462.94, 4024.06, 4251.76]</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>[1838.78, 2299.68, 2542.07]</t>
+          <t>[6364.54, 3964.6, 3055.77]</t>
         </is>
       </c>
     </row>
@@ -7020,41 +7020,41 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(1, 1, 0)</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>740.3200000000001</v>
+        <v>665.5700000000001</v>
       </c>
       <c r="G144" t="n">
-        <v>656.87</v>
+        <v>428.68</v>
       </c>
       <c r="H144" t="n">
-        <v>26.77</v>
+        <v>13.28</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>[3308.84, 3308.84, 3308.84]</t>
+          <t>[3986.74, 4202.38, 6582.22]</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>[2299.68, 2542.07, 3114.16]</t>
+          <t>[3964.6, 3055.77, 6699.51]</t>
         </is>
       </c>
     </row>
@@ -7066,41 +7066,41 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>(5, 0, 3)</t>
+          <t>(1, 1, 0)</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>1175.62</v>
+        <v>659.1799999999999</v>
       </c>
       <c r="G145" t="n">
-        <v>1122.8</v>
+        <v>429.51</v>
       </c>
       <c r="H145" t="n">
-        <v>30.31</v>
+        <v>13.39</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>[1301.23, 2464.69, 5475.67]</t>
+          <t>[4188.19, 6554.37, 1154.54]</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>[2542.07, 3114.16, 6953.75]</t>
+          <t>[3055.77, 6699.51, 1165.51]</t>
         </is>
       </c>
     </row>
@@ -7112,41 +7112,41 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(0, 1, 0)</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>2173.8</v>
+        <v>1208.97</v>
       </c>
       <c r="G146" t="n">
-        <v>1437.14</v>
+        <v>975.97</v>
       </c>
       <c r="H146" t="n">
-        <v>23.29</v>
+        <v>31.97</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>[3219.79, 3219.79, 3219.79]</t>
+          <t>[4716.35, 746.24, 1207.43]</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>[3114.16, 6953.75, 3691.63]</t>
+          <t>[6699.51, 1165.51, 1732.91]</t>
         </is>
       </c>
     </row>
@@ -7158,17 +7158,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(1, 1, 0)</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -7177,22 +7177,22 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>564.41</v>
+        <v>222.99</v>
       </c>
       <c r="G147" t="n">
-        <v>509.32</v>
+        <v>183.07</v>
       </c>
       <c r="H147" t="n">
-        <v>9.02</v>
+        <v>10.86</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>[6106.68, 3407.43, 5139.56]</t>
+          <t>[958.62, 1749.49, 2021.78]</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>[6953.75, 3691.63, 5536.26]</t>
+          <t>[1165.51, 1732.91, 2347.51]</t>
         </is>
       </c>
     </row>
@@ -7204,17 +7204,17 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(1, 1, 0)</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -7223,22 +7223,22 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>156.17</v>
+        <v>86.34999999999999</v>
       </c>
       <c r="G148" t="n">
-        <v>151.08</v>
+        <v>54.37</v>
       </c>
       <c r="H148" t="n">
-        <v>2.93</v>
+        <v>3.05</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>[3811.9, 5662.33, 6571.43]</t>
+          <t>[1881.81, 2347.46, 2597.9]</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>[3691.63, 5536.26, 6364.54]</t>
+          <t>[1732.91, 2347.51, 2583.73]</t>
         </is>
       </c>
     </row>
@@ -7250,17 +7250,17 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>(1, 1, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -7269,22 +7269,22 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>116.73</v>
+        <v>381.95</v>
       </c>
       <c r="G149" t="n">
-        <v>112.44</v>
+        <v>371.41</v>
       </c>
       <c r="H149" t="n">
-        <v>2.16</v>
+        <v>13.55</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>[5615.67, 6519.12, 4067.94]</t>
+          <t>[2068.68, 2240.11, 2688.3]</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>[5536.26, 6364.54, 3964.6]</t>
+          <t>[2347.51, 2583.73, 3180.08]</t>
         </is>
       </c>
     </row>
@@ -7296,17 +7296,17 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>(1, 1, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -7315,22 +7315,22 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>693.6900000000001</v>
+        <v>635.55</v>
       </c>
       <c r="G150" t="n">
-        <v>451.28</v>
+        <v>415.27</v>
       </c>
       <c r="H150" t="n">
-        <v>14.06</v>
+        <v>8.01</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>[6462.94, 4024.06, 4251.76]</t>
+          <t>[2522.85, 3090.62, 6901.18]</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>[6364.54, 3964.6, 3055.77]</t>
+          <t>[2583.73, 3180.08, 5805.7]</t>
         </is>
       </c>
     </row>
@@ -7342,17 +7342,17 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>(1, 1, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -7361,22 +7361,22 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>665.5700000000001</v>
+        <v>1528.06</v>
       </c>
       <c r="G151" t="n">
-        <v>428.68</v>
+        <v>1200.14</v>
       </c>
       <c r="H151" t="n">
-        <v>13.28</v>
+        <v>20.3</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>[3986.74, 4202.38, 6582.22]</t>
+          <t>[3130.63, 6990.52, 3711.15]</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>[3964.6, 3055.77, 6699.51]</t>
+          <t>[3180.08, 5805.7, 6077.3]</t>
         </is>
       </c>
     </row>
@@ -7388,41 +7388,41 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>(0, 0, 2)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>623.61</v>
+        <v>24.13</v>
       </c>
       <c r="G152" t="n">
-        <v>555.17</v>
+        <v>23.47</v>
       </c>
       <c r="H152" t="n">
-        <v>49.28</v>
+        <v>1.62</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>[827.32, 1977.97, 1096.94]</t>
+          <t>[1597.13, 1952.86, 1188.43]</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>[1226.1, 1024.19, 1409.9]</t>
+          <t>[1580.6, 1976.4, 1158.11]</t>
         </is>
       </c>
     </row>
@@ -7434,41 +7434,41 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>(0, 0, 2)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>548.5</v>
+        <v>77.62</v>
       </c>
       <c r="G153" t="n">
-        <v>444.64</v>
+        <v>61.06</v>
       </c>
       <c r="H153" t="n">
-        <v>88.22</v>
+        <v>4.32</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>[1602.35, 1411.81, 1116.16]</t>
+          <t>[1951.5, 1187.61, 1535.69]</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>[1024.19, 1409.9, 362.31]</t>
+          <t>[1976.4, 1158.11, 1406.9]</t>
         </is>
       </c>
     </row>
@@ -7480,41 +7480,41 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>(3, 0, 4)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>1112.62</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="G154" t="n">
-        <v>970.2</v>
+        <v>56.03</v>
       </c>
       <c r="H154" t="n">
-        <v>165.3</v>
+        <v>4.05</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>[3127.1, 796.47, 1057.85]</t>
+          <t>[1188.55, 1536.9, 2875.44]</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>[1409.9, 362.31, 298.6]</t>
+          <t>[1158.11, 1406.9, 2867.79]</t>
         </is>
       </c>
     </row>
@@ -7526,41 +7526,41 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>(0, 0, 2)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(1, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>1259.12</v>
+        <v>94.04000000000001</v>
       </c>
       <c r="G155" t="n">
-        <v>1072.84</v>
+        <v>82.58</v>
       </c>
       <c r="H155" t="n">
-        <v>146.63</v>
+        <v>6.02</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>[910.79, 966.25, 1082.17]</t>
+          <t>[1498.77, 2891.24, 1369.75]</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>[362.31, 298.6, 3084.55]</t>
+          <t>[1406.9, 2867.79, 1237.31]</t>
         </is>
       </c>
     </row>
@@ -7572,41 +7572,41 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>(0, 0, 2)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>1649.56</v>
+        <v>78.48999999999999</v>
       </c>
       <c r="G156" t="n">
-        <v>1474.1</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="H156" t="n">
-        <v>270.17</v>
+        <v>3.79</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>[1411.03, 578.73, 1029.45]</t>
+          <t>[2744.21, 1279.87, 995.02]</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>[298.6, 3084.55, 225.4]</t>
+          <t>[2867.79, 1237.31, 1032.43]</t>
         </is>
       </c>
     </row>
@@ -7618,12 +7618,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -7633,26 +7633,26 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>20.55</v>
+        <v>72.22</v>
       </c>
       <c r="G157" t="n">
-        <v>19.07</v>
+        <v>61.72</v>
       </c>
       <c r="H157" t="n">
-        <v>2.09</v>
+        <v>4.95</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>[3056.67, 234.65, 1600.69]</t>
+          <t>[1351.15, 1059.62, 1426.13]</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>[3084.55, 225.4, 1580.6]</t>
+          <t>[1237.31, 1032.43, 1470.26]</t>
         </is>
       </c>
     </row>
@@ -7664,12 +7664,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -7679,26 +7679,26 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>16.89</v>
+        <v>32.96</v>
       </c>
       <c r="G158" t="n">
-        <v>16.15</v>
+        <v>27.44</v>
       </c>
       <c r="H158" t="n">
-        <v>2.14</v>
+        <v>2.88</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>[234.82, 1601.81, 1958.57]</t>
+          <t>[1047.78, 1417.02, 373.0]</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>[225.4, 1580.6, 1976.4]</t>
+          <t>[1032.43, 1470.26, 386.71]</t>
         </is>
       </c>
     </row>
@@ -7710,12 +7710,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -7725,26 +7725,26 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>24.13</v>
+        <v>36.1</v>
       </c>
       <c r="G159" t="n">
-        <v>23.47</v>
+        <v>31.35</v>
       </c>
       <c r="H159" t="n">
-        <v>1.62</v>
+        <v>4.63</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>[1597.13, 1952.86, 1188.43]</t>
+          <t>[1414.26, 372.63, 348.04]</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>[1580.6, 1976.4, 1158.11]</t>
+          <t>[1470.26, 386.71, 372.01]</t>
         </is>
       </c>
     </row>
@@ -7756,12 +7756,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -7771,26 +7771,26 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>77.62</v>
+        <v>23.1</v>
       </c>
       <c r="G160" t="n">
-        <v>61.06</v>
+        <v>22.05</v>
       </c>
       <c r="H160" t="n">
-        <v>4.32</v>
+        <v>3.54</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>[1951.5, 1187.61, 1535.69]</t>
+          <t>[373.78, 348.44, 3150.72]</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>[1976.4, 1158.11, 1406.9]</t>
+          <t>[386.71, 372.01, 3180.35]</t>
         </is>
       </c>
     </row>
@@ -7802,12 +7802,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -7817,26 +7817,26 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>77.20999999999999</v>
+        <v>22.67</v>
       </c>
       <c r="G161" t="n">
-        <v>56.03</v>
+        <v>22.59</v>
       </c>
       <c r="H161" t="n">
-        <v>4.05</v>
+        <v>5.31</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>[1188.55, 1536.9, 2875.44]</t>
+          <t>[350.71, 3159.14, 239.31]</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>[1158.11, 1406.9, 2867.79]</t>
+          <t>[372.01, 3180.35, 264.57]</t>
         </is>
       </c>
     </row>
@@ -7848,41 +7848,41 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>3989.8</v>
+        <v>110.77</v>
       </c>
       <c r="G162" t="n">
-        <v>3954.35</v>
+        <v>100.04</v>
       </c>
       <c r="H162" t="n">
-        <v>569.13</v>
+        <v>8.92</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>[6136.43, 4990.39, 4078.33]</t>
+          <t>[1012.53, 1882.29, 727.01]</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>[2131.2, 413.0, 797.9]</t>
+          <t>[944.9, 1715.0, 661.8]</t>
         </is>
       </c>
     </row>
@@ -7894,12 +7894,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -7909,26 +7909,26 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>504.95</v>
+        <v>115.59</v>
       </c>
       <c r="G163" t="n">
-        <v>467.18</v>
+        <v>108.6</v>
       </c>
       <c r="H163" t="n">
-        <v>110.86</v>
+        <v>10.4</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>[995.08, 995.08, 995.08]</t>
+          <t>[1873.64, 723.67, 941.9]</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>[413.0, 797.9, 372.8]</t>
+          <t>[1715.0, 661.8, 836.6]</t>
         </is>
       </c>
     </row>
@@ -7940,41 +7940,41 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>466.68</v>
+        <v>243.3</v>
       </c>
       <c r="G164" t="n">
-        <v>425.71</v>
+        <v>172.04</v>
       </c>
       <c r="H164" t="n">
-        <v>101.84</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>[954.27, 954.27, 954.27]</t>
+          <t>[613.7, 783.93, 3523.67]</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>[797.9, 372.8, 415.0]</t>
+          <t>[661.8, 836.6, 3939.0]</t>
         </is>
       </c>
     </row>
@@ -7986,41 +7986,41 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>560.41</v>
+        <v>236.36</v>
       </c>
       <c r="G165" t="n">
-        <v>560.05</v>
+        <v>199.88</v>
       </c>
       <c r="H165" t="n">
-        <v>106.59</v>
+        <v>7.83</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>[946.54, 946.54, 946.54]</t>
+          <t>[798.05, 3592.48, 1911.43]</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>[372.8, 415.0, 1521.4]</t>
+          <t>[836.6, 3939.0, 2126.0]</t>
         </is>
       </c>
     </row>
@@ -8032,41 +8032,41 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>177.5</v>
+        <v>212.03</v>
       </c>
       <c r="G166" t="n">
-        <v>125.12</v>
+        <v>182.41</v>
       </c>
       <c r="H166" t="n">
-        <v>10.63</v>
+        <v>9.27</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>[434.13, 1219.39, 782.82]</t>
+          <t>[3629.88, 1932.91, 368.46]</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>[415.0, 1521.4, 728.6]</t>
+          <t>[3939.0, 2126.0, 413.5]</t>
         </is>
       </c>
     </row>
@@ -8078,17 +8078,17 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -8097,22 +8097,22 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>117.26</v>
+        <v>106.2</v>
       </c>
       <c r="G167" t="n">
-        <v>110.41</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="H167" t="n">
-        <v>10.32</v>
+        <v>9.02</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>[1687.69, 810.58, 1027.85]</t>
+          <t>[1965.6, 375.16, 713.84]</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>[1521.4, 728.6, 944.9]</t>
+          <t>[2126.0, 413.5, 795.3]</t>
         </is>
       </c>
     </row>
@@ -8124,17 +8124,17 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -8143,22 +8143,22 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>120.99</v>
+        <v>49.33</v>
       </c>
       <c r="G168" t="n">
-        <v>110.31</v>
+        <v>46.68</v>
       </c>
       <c r="H168" t="n">
-        <v>9.6</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>[804.13, 1019.69, 1895.6]</t>
+          <t>[381.3, 726.4, 334.66]</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>[728.6, 944.9, 1715.0]</t>
+          <t>[413.5, 795.3, 373.6]</t>
         </is>
       </c>
     </row>
@@ -8170,17 +8170,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -8189,22 +8189,22 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>110.77</v>
+        <v>45.43</v>
       </c>
       <c r="G169" t="n">
-        <v>100.04</v>
+        <v>44.31</v>
       </c>
       <c r="H169" t="n">
-        <v>8.92</v>
+        <v>8.76</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>[1012.53, 1882.29, 727.01]</t>
+          <t>[737.69, 340.22, 373.85]</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>[944.9, 1715.0, 661.8]</t>
+          <t>[795.3, 373.6, 415.8]</t>
         </is>
       </c>
     </row>
@@ -8216,17 +8216,17 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -8235,22 +8235,22 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>115.59</v>
+        <v>70.22</v>
       </c>
       <c r="G170" t="n">
-        <v>108.6</v>
+        <v>56.01</v>
       </c>
       <c r="H170" t="n">
-        <v>10.4</v>
+        <v>6.94</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>[1873.64, 723.67, 941.9]</t>
+          <t>[351.1, 386.05, 1397.94]</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>[1715.0, 661.8, 836.6]</t>
+          <t>[373.6, 415.8, 1513.7]</t>
         </is>
       </c>
     </row>
@@ -8262,12 +8262,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -8281,22 +8281,22 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>243.3</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="G171" t="n">
-        <v>172.04</v>
+        <v>59.71</v>
       </c>
       <c r="H171" t="n">
-        <v>8.039999999999999</v>
+        <v>6.84</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>[613.7, 783.93, 3523.67]</t>
+          <t>[394.7, 1430.29, 677.06]</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>[661.8, 836.6, 3939.0]</t>
+          <t>[415.8, 1513.7, 751.7]</t>
         </is>
       </c>
     </row>
@@ -8308,17 +8308,17 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 1, 1)</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -8327,22 +8327,22 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>773.3</v>
+        <v>1533.73</v>
       </c>
       <c r="G172" t="n">
-        <v>630.64</v>
+        <v>1281.06</v>
       </c>
       <c r="H172" t="n">
-        <v>43.72</v>
+        <v>48.48</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>[2710.89, 1686.3, 1830.35]</t>
+          <t>[2810.14, 5221.36, 3619.91]</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>[1473.51, 1514.97, 1347.13]</t>
+          <t>[2132.52, 2747.67, 2928.02]</t>
         </is>
       </c>
     </row>
@@ -8354,17 +8354,17 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>(1, 1, 1)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -8373,22 +8373,22 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>452.99</v>
+        <v>1176.79</v>
       </c>
       <c r="G173" t="n">
-        <v>378.45</v>
+        <v>867.46</v>
       </c>
       <c r="H173" t="n">
-        <v>23.44</v>
+        <v>31.17</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>[1390.86, 1641.95, 2496.71]</t>
+          <t>[4723.47, 3406.28, 2663.61]</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>[1514.97, 1347.13, 1780.28]</t>
+          <t>[2747.67, 2928.02, 2811.94]</t>
         </is>
       </c>
     </row>
@@ -8400,41 +8400,41 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>(1, 1, 1)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>472.01</v>
+        <v>432.08</v>
       </c>
       <c r="G174" t="n">
-        <v>375.02</v>
+        <v>338.96</v>
       </c>
       <c r="H174" t="n">
-        <v>23.01</v>
+        <v>8.68</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>[1681.86, 2524.74, 1996.75]</t>
+          <t>[2804.93, 2634.76, 3898.54]</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>[1347.13, 1780.28, 1950.87]</t>
+          <t>[2928.02, 2811.94, 4615.15]</t>
         </is>
       </c>
     </row>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -8461,26 +8461,26 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>1036.03</v>
+        <v>432.04</v>
       </c>
       <c r="G175" t="n">
-        <v>771.33</v>
+        <v>353.83</v>
       </c>
       <c r="H175" t="n">
-        <v>23.08</v>
+        <v>11.17</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>[2308.28, 1878.37, 3062.85]</t>
+          <t>[2667.31, 3913.05, 1846.53]</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>[1780.28, 1950.87, 4776.34]</t>
+          <t>[2811.94, 4615.15, 1631.78]</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -8511,22 +8511,22 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>1150.68</v>
+        <v>394.91</v>
       </c>
       <c r="G176" t="n">
-        <v>932.02</v>
+        <v>311.16</v>
       </c>
       <c r="H176" t="n">
-        <v>26.46</v>
+        <v>10.64</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>[1680.78, 2917.97, 1840.91]</t>
+          <t>[3972.9, 1857.93, 1630.66]</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>[1950.87, 4776.34, 2508.52]</t>
+          <t>[4615.15, 1631.78, 1565.58]</t>
         </is>
       </c>
     </row>
@@ -8538,12 +8538,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -8557,22 +8557,22 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>1101.74</v>
+        <v>246.02</v>
       </c>
       <c r="G177" t="n">
-        <v>940.08</v>
+        <v>225.1</v>
       </c>
       <c r="H177" t="n">
-        <v>27.5</v>
+        <v>13.33</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>[3032.11, 1869.91, 2569.9]</t>
+          <t>[1944.74, 1651.92, 1528.73]</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>[4776.34, 2508.52, 2132.52]</t>
+          <t>[1631.78, 1565.58, 1804.74]</t>
         </is>
       </c>
     </row>
@@ -8584,12 +8584,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -8599,26 +8599,26 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>1320.78</v>
+        <v>342.39</v>
       </c>
       <c r="G178" t="n">
-        <v>1003.18</v>
+        <v>275.88</v>
       </c>
       <c r="H178" t="n">
-        <v>38.61</v>
+        <v>17</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>[2214.21, 2635.61, 4959.83]</t>
+          <t>[1581.75, 1504.38, 2044.32]</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>[2508.52, 2132.52, 2747.67]</t>
+          <t>[1565.58, 1804.74, 1533.22]</t>
         </is>
       </c>
     </row>
@@ -8630,41 +8630,41 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>(1, 1, 1)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>1533.73</v>
+        <v>434</v>
       </c>
       <c r="G179" t="n">
-        <v>1281.06</v>
+        <v>425.09</v>
       </c>
       <c r="H179" t="n">
-        <v>48.48</v>
+        <v>26.38</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>[2810.14, 5221.36, 3619.91]</t>
+          <t>[1500.28, 2042.69, 2050.63]</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>[2132.52, 2747.67, 2928.02]</t>
+          <t>[1804.74, 1533.22, 1589.3]</t>
         </is>
       </c>
     </row>
@@ -8676,12 +8676,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -8691,26 +8691,26 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>1176.79</v>
+        <v>808.95</v>
       </c>
       <c r="G180" t="n">
-        <v>867.46</v>
+        <v>754.77</v>
       </c>
       <c r="H180" t="n">
-        <v>31.17</v>
+        <v>35.23</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>[4723.47, 3406.28, 2663.61]</t>
+          <t>[2147.9, 2078.89, 4492.63]</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>[2747.67, 2928.02, 2811.94]</t>
+          <t>[1533.22, 1589.3, 3332.59]</t>
         </is>
       </c>
     </row>
@@ -8722,12 +8722,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -8737,26 +8737,26 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(1, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>432.08</v>
+        <v>558.72</v>
       </c>
       <c r="G181" t="n">
-        <v>338.96</v>
+        <v>421.05</v>
       </c>
       <c r="H181" t="n">
-        <v>8.68</v>
+        <v>16.27</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>[2804.93, 2634.76, 3898.54]</t>
+          <t>[1908.94, 4245.49, 2356.42]</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>[2928.02, 2811.94, 4615.15]</t>
+          <t>[1589.3, 3332.59, 2325.81]</t>
         </is>
       </c>
     </row>
@@ -8768,12 +8768,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -8787,22 +8787,22 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>36.8</v>
+        <v>14.23</v>
       </c>
       <c r="G182" t="n">
-        <v>34.66</v>
+        <v>9.91</v>
       </c>
       <c r="H182" t="n">
-        <v>7.77</v>
+        <v>0.49</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>[954.82, 316.25, 425.66]</t>
+          <t>[2433.86, 2009.5, 834.39]</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>[977.96, 287.25, 477.49]</t>
+          <t>[2428.74, 2033.61, 833.88]</t>
         </is>
       </c>
     </row>
@@ -8814,17 +8814,17 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -8833,22 +8833,22 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>58.17</v>
+        <v>17.63</v>
       </c>
       <c r="G183" t="n">
-        <v>53.11</v>
+        <v>14.23</v>
       </c>
       <c r="H183" t="n">
-        <v>12.08</v>
+        <v>0.96</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>[306.91, 410.04, 400.26]</t>
+          <t>[2008.54, 834.08, 1085.9]</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>[287.25, 477.49, 472.46]</t>
+          <t>[2033.61, 833.88, 1068.47]</t>
         </is>
       </c>
     </row>
@@ -8860,17 +8860,17 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -8879,22 +8879,22 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>70.97</v>
+        <v>11.62</v>
       </c>
       <c r="G184" t="n">
-        <v>70.61</v>
+        <v>8.34</v>
       </c>
       <c r="H184" t="n">
-        <v>14.65</v>
+        <v>0.78</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>[404.32, 394.67, 439.89]</t>
+          <t>[836.43, 1088.25, 1526.33]</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>[477.49, 472.46, 500.77]</t>
+          <t>[833.88, 1068.47, 1523.63]</t>
         </is>
       </c>
     </row>
@@ -8906,17 +8906,17 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -8925,22 +8925,22 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>66.31999999999999</v>
+        <v>58.57</v>
       </c>
       <c r="G185" t="n">
-        <v>64.44</v>
+        <v>40.18</v>
       </c>
       <c r="H185" t="n">
-        <v>9.48</v>
+        <v>3.71</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>[408.46, 455.26, 1361.56]</t>
+          <t>[1087.5, 1525.52, 980.42]</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>[472.46, 500.77, 1445.38]</t>
+          <t>[1068.47, 1523.63, 1080.05]</t>
         </is>
       </c>
     </row>
@@ -8952,12 +8952,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -8971,22 +8971,22 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>22.6</v>
+        <v>60.43</v>
       </c>
       <c r="G186" t="n">
-        <v>17.51</v>
+        <v>42.28</v>
       </c>
       <c r="H186" t="n">
-        <v>1.64</v>
+        <v>5.43</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>[485.83, 1446.82, 1997.06]</t>
+          <t>[1519.45, 977.41, 287.13]</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>[500.77, 1445.38, 1960.9]</t>
+          <t>[1523.63, 1080.05, 307.15]</t>
         </is>
       </c>
     </row>
@@ -8998,12 +8998,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -9017,22 +9017,22 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>30.44</v>
+        <v>79.97</v>
       </c>
       <c r="G187" t="n">
-        <v>26.51</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="H187" t="n">
-        <v>1.36</v>
+        <v>10.67</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>[1457.21, 2007.95, 2449.39]</t>
+          <t>[978.02, 287.26, 477.51]</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>[1445.38, 1960.9, 2428.74]</t>
+          <t>[1080.05, 307.15, 569.05]</t>
         </is>
       </c>
     </row>
@@ -9044,12 +9044,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -9063,22 +9063,22 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>28.53</v>
+        <v>54.89</v>
       </c>
       <c r="G188" t="n">
-        <v>25.64</v>
+        <v>46.85</v>
       </c>
       <c r="H188" t="n">
-        <v>1.24</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>[2004.22, 2445.93, 2017.18]</t>
+          <t>[293.75, 485.82, 478.81]</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>[1960.9, 2428.74, 2033.61]</t>
+          <t>[307.15, 569.05, 522.74]</t>
         </is>
       </c>
     </row>
@@ -9090,12 +9090,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -9109,22 +9109,22 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>14.23</v>
+        <v>50.79</v>
       </c>
       <c r="G189" t="n">
-        <v>9.91</v>
+        <v>40.38</v>
       </c>
       <c r="H189" t="n">
-        <v>0.49</v>
+        <v>7.32</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>[2433.86, 2009.5, 834.39]</t>
+          <t>[490.82, 482.6, 509.04]</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>[2428.74, 2033.61, 833.88]</t>
+          <t>[569.05, 522.74, 506.27]</t>
         </is>
       </c>
     </row>
@@ -9136,12 +9136,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -9155,22 +9155,22 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>17.63</v>
+        <v>23.57</v>
       </c>
       <c r="G190" t="n">
-        <v>14.23</v>
+        <v>23.01</v>
       </c>
       <c r="H190" t="n">
-        <v>0.96</v>
+        <v>3.21</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>[2008.54, 834.08, 1085.9]</t>
+          <t>[499.85, 523.06, 1494.84]</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>[2033.61, 833.88, 1068.47]</t>
+          <t>[522.74, 506.27, 1524.19]</t>
         </is>
       </c>
     </row>
@@ -9182,12 +9182,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -9201,22 +9201,22 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>11.62</v>
+        <v>16.34</v>
       </c>
       <c r="G191" t="n">
-        <v>8.34</v>
+        <v>14.52</v>
       </c>
       <c r="H191" t="n">
-        <v>0.78</v>
+        <v>1.93</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>[836.43, 1088.25, 1526.33]</t>
+          <t>[528.96, 1507.9, 2026.17]</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>[833.88, 1068.47, 1523.63]</t>
+          <t>[506.27, 1524.19, 2030.74]</t>
         </is>
       </c>
     </row>
@@ -9228,12 +9228,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -9247,22 +9247,22 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>697.37</v>
+        <v>262.34</v>
       </c>
       <c r="G192" t="n">
-        <v>628.14</v>
+        <v>229</v>
       </c>
       <c r="H192" t="n">
-        <v>26.46</v>
+        <v>8.82</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>[2548.95, 2936.95, 3442.31]</t>
+          <t>[2308.59, 3612.29, 4410.68]</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>[2303.08, 2285.14, 2455.58]</t>
+          <t>[1955.9, 3893.88, 4357.98]</t>
         </is>
       </c>
     </row>
@@ -9274,12 +9274,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -9289,26 +9289,26 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F193" t="n">
-        <v>804.3200000000001</v>
+        <v>522.64</v>
       </c>
       <c r="G193" t="n">
-        <v>784.83</v>
+        <v>442.64</v>
       </c>
       <c r="H193" t="n">
-        <v>34.69</v>
+        <v>10.03</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>[2822.41, 3386.21, 2964.9]</t>
+          <t>[3094.55, 4236.54, 5591.5]</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>[2285.14, 2455.58, 2078.31]</t>
+          <t>[3893.88, 4357.98, 5998.64]</t>
         </is>
       </c>
     </row>
@@ -9320,12 +9320,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -9339,22 +9339,22 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>616.65</v>
+        <v>1423.37</v>
       </c>
       <c r="G194" t="n">
-        <v>540.4</v>
+        <v>956.23</v>
       </c>
       <c r="H194" t="n">
-        <v>24.42</v>
+        <v>12.58</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>[3199.17, 2835.52, 1957.17]</t>
+          <t>[4771.56, 5973.82, 6303.25]</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>[2455.58, 2078.31, 1836.76]</t>
+          <t>[4357.98, 5998.64, 8733.53]</t>
         </is>
       </c>
     </row>
@@ -9366,12 +9366,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -9385,22 +9385,22 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>504.35</v>
+        <v>1416.28</v>
       </c>
       <c r="G195" t="n">
-        <v>410.25</v>
+        <v>984.05</v>
       </c>
       <c r="H195" t="n">
-        <v>18.91</v>
+        <v>12.86</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>[2531.85, 1868.03, 2992.78]</t>
+          <t>[5543.81, 6324.61, 2510.35]</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>[2078.31, 1836.76, 2246.84]</t>
+          <t>[5998.64, 8733.53, 2598.76]</t>
         </is>
       </c>
     </row>
@@ -9412,41 +9412,41 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>424.83</v>
+        <v>1442.71</v>
       </c>
       <c r="G196" t="n">
-        <v>399.94</v>
+        <v>922.35</v>
       </c>
       <c r="H196" t="n">
-        <v>19</v>
+        <v>12.94</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>[1639.23, 2756.55, 2583.86]</t>
+          <t>[6242.74, 2492.62, 2562.13]</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>[1836.76, 2246.84, 2091.29]</t>
+          <t>[8733.53, 2598.76, 2732.23]</t>
         </is>
       </c>
     </row>
@@ -9458,12 +9458,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -9473,26 +9473,26 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>661.97</v>
+        <v>162.54</v>
       </c>
       <c r="G197" t="n">
-        <v>660.05</v>
+        <v>128.3</v>
       </c>
       <c r="H197" t="n">
-        <v>31.57</v>
+        <v>4.86</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>[2937.42, 2680.26, 2656.5]</t>
+          <t>[2856.93, 2621.06, 2711.09]</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>[2246.84, 2091.29, 1955.9]</t>
+          <t>[2598.76, 2732.23, 2726.66]</t>
         </is>
       </c>
     </row>
@@ -9504,12 +9504,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -9519,26 +9519,26 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>332.62</v>
+        <v>252.24</v>
       </c>
       <c r="G198" t="n">
-        <v>295.3</v>
+        <v>225.8</v>
       </c>
       <c r="H198" t="n">
-        <v>13.62</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>[2329.66, 2460.55, 3751.02]</t>
+          <t>[2496.98, 2643.03, 2221.17]</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>[2091.29, 1955.9, 3893.88]</t>
+          <t>[2732.23, 2726.66, 2579.69]</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -9565,26 +9565,26 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>262.34</v>
+        <v>185.02</v>
       </c>
       <c r="G199" t="n">
-        <v>229</v>
+        <v>140.47</v>
       </c>
       <c r="H199" t="n">
-        <v>8.82</v>
+        <v>5.78</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>[2308.59, 3612.29, 4410.68]</t>
+          <t>[2761.67, 2270.7, 1979.53]</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>[1955.9, 3893.88, 4357.98]</t>
+          <t>[2726.66, 2579.69, 1902.11]</t>
         </is>
       </c>
     </row>
@@ -9596,12 +9596,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -9611,26 +9611,26 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F200" t="n">
-        <v>522.64</v>
+        <v>221.3</v>
       </c>
       <c r="G200" t="n">
-        <v>442.64</v>
+        <v>195.95</v>
       </c>
       <c r="H200" t="n">
-        <v>10.03</v>
+        <v>8.34</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>[3094.55, 4236.54, 5591.5]</t>
+          <t>[2256.58, 1973.32, 2401.87]</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>[3893.88, 4357.98, 5998.64]</t>
+          <t>[2579.69, 1902.11, 2208.35]</t>
         </is>
       </c>
     </row>
@@ -9642,12 +9642,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -9657,26 +9657,26 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>1423.37</v>
+        <v>282.23</v>
       </c>
       <c r="G201" t="n">
-        <v>956.23</v>
+        <v>257.3</v>
       </c>
       <c r="H201" t="n">
-        <v>12.58</v>
+        <v>12.04</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>[4771.56, 5973.82, 6303.25]</t>
+          <t>[2091.8, 2628.85, 2434.47]</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>[4357.98, 5998.64, 8733.53]</t>
+          <t>[1902.11, 2208.35, 2272.74]</t>
         </is>
       </c>
     </row>
